--- a/bundles/core_workbooks/AIHE_Core_Resource_Workbooks_V1.0.xlsx
+++ b/bundles/core_workbooks/AIHE_Core_Resource_Workbooks_V1.0.xlsx
@@ -2,32 +2,32 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="1" r:id="Rf50648d7e646431b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resource Index" sheetId="2" r:id="R8467163c299a4f76"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIHE-A01" sheetId="3" r:id="R6e3a8147e9384a4f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIHE-A02" sheetId="4" r:id="R57c358d80bea4a16"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIHE-A03" sheetId="5" r:id="Ra0c100bdd0864c0f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIHE-A04" sheetId="6" r:id="R0ad4b3e443b54e70"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIHE-C04" sheetId="7" r:id="R61db4fd9ab4745f0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIHE-B03" sheetId="8" r:id="Rade535e9491643d5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIHE-C01" sheetId="9" r:id="Rc8bd5d31383c4af5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIHE-C02" sheetId="10" r:id="Rbd3aea9a248a486b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIHE-B01" sheetId="11" r:id="Rf15421379bf344be"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIHE-B02" sheetId="12" r:id="Rd3b3a57f06744335"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIHE-B04" sheetId="13" r:id="R76b262fa394c40d7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIHE-B05" sheetId="14" r:id="R5daa69c8183c4120"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIHE-D01" sheetId="15" r:id="R1c9d2e055268417a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIHE-C03" sheetId="16" r:id="R55cf6ae2a0d94443"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIHE-C05" sheetId="17" r:id="Raff5d60591524ad1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIHE-D02" sheetId="18" r:id="Ra4207bd87aba4944"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIHE-D03" sheetId="19" r:id="R27f8002ef620438c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIHE-D04" sheetId="20" r:id="R02b6955fda164ea9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIHE-D05" sheetId="21" r:id="R9e91fc993c354fb9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIHE-E01" sheetId="22" r:id="Ra59b7c750a124e92"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIHE-E02" sheetId="23" r:id="R7d531e21eda84a0b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIHE-E03" sheetId="24" r:id="Rc14dcc259a574add"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIHE-E04" sheetId="25" r:id="R9895d1c82a014816"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIHE-E05" sheetId="26" r:id="R99d56490eee949c3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="1" r:id="Ra7e5f7ab379a49ae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resource Index" sheetId="2" r:id="Rbdd77b162bdb4241"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIHE-A01" sheetId="3" r:id="R5b292742709f483a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIHE-A02" sheetId="4" r:id="R42337ffd57c44781"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIHE-A03" sheetId="5" r:id="Rf5a6d1a624824171"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIHE-A04" sheetId="6" r:id="R25edb7735a0049ea"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIHE-C04" sheetId="7" r:id="Rc34e892ed1cc4893"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIHE-B03" sheetId="8" r:id="R75393290ebf74e3e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIHE-C01" sheetId="9" r:id="R9172ed372ce24725"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIHE-C02" sheetId="10" r:id="R6db1755ee7b54b86"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIHE-B01" sheetId="11" r:id="Rc190152eda0b4d3e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIHE-B02" sheetId="12" r:id="Rc77eaf41cea64faf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIHE-B04" sheetId="13" r:id="R103bb2cc9ebf446d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIHE-B05" sheetId="14" r:id="R513170b0281b4fad"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIHE-D01" sheetId="15" r:id="Re19b7de0bf7e45cc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIHE-C03" sheetId="16" r:id="R23ccddf93e20485b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIHE-C05" sheetId="17" r:id="Rc3b041b10e874837"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIHE-D02" sheetId="18" r:id="R4f85c094d0d0457c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIHE-D03" sheetId="19" r:id="R668e182ae9f549cd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIHE-D04" sheetId="20" r:id="Rd298a82f43d94e2d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIHE-D05" sheetId="21" r:id="R011cfba3f8444f7b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIHE-E01" sheetId="22" r:id="Rcb37900c56274adf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIHE-E02" sheetId="23" r:id="Rf557bd671a064265"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIHE-E03" sheetId="24" r:id="Rde6db18b0d41440c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIHE-E04" sheetId="25" r:id="Rb04e9a91416f4939"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIHE-E05" sheetId="26" r:id="Rdd5ee2abf0e6474c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -38,7 +38,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="5">
+  <x:fonts count="21">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -66,8 +66,99 @@
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:i/>
+      <x:sz val="13"/>
+      <x:color rgb="FF7B1734"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="14"/>
+      <x:color rgb="FF183B56"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF7B1734"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF7B1734"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="9"/>
+      <x:color rgb="FF5F5A5B"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:sz val="9"/>
+      <x:color rgb="FF5F5A5B"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="12"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF20232A"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="14"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:i/>
+      <x:sz val="11"/>
+      <x:color rgb="FF7B1734"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF183B56"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FF7B1734"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="FF7B1734"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="8"/>
+      <x:color rgb="FF5F5A5B"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:sz val="8"/>
+      <x:color rgb="FF5F5A5B"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FF183B56"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="5">
+  <x:fills count="17">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -89,6 +180,66 @@
         <x:fgColor rgb="FF183B56"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF7B1734"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF7F1E7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFDF8"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF183B56"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF7B1734"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF7F1E7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFDF8"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF183B56"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF7B1734"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF7F1E7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFDF8"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF183B56"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="2">
     <x:border/>
@@ -97,43 +248,43 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="36">
+  <x:cellXfs count="135">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center"/>
+      <x:alignment horizontal="centre"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
+      <x:alignment horizontal="centre" vertical="centre"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center"/>
+      <x:alignment horizontal="centre"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
+      <x:alignment horizontal="centre" vertical="centre"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center"/>
+      <x:alignment horizontal="centre"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center"/>
+      <x:alignment horizontal="centre"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" wrapText="1"/>
+      <x:alignment horizontal="centre" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" wrapText="1"/>
+      <x:alignment horizontal="centre" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
@@ -144,7 +295,7 @@
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" wrapText="1"/>
+      <x:alignment horizontal="centre" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -152,15 +303,15 @@
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" wrapText="1"/>
+      <x:alignment horizontal="centre" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center"/>
+      <x:alignment horizontal="centre"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center"/>
+      <x:alignment horizontal="centre"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
@@ -173,6 +324,279 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="centre" vertical="centre"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="centre"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="centre" vertical="centre"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="centre" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="centre" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="centre"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="centre" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="centre" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="centre"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="centre" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="10" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="centre" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="centre"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="centre" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="11" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="centre" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="11" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="centre" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="centre" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="centre"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="centre" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="centre" vertical="centre" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="centre"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="centre"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="centre" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="centre" vertical="centre" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="centre" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="centre" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="centre" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="centre" vertical="centre" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="centre"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="centre" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="centre" vertical="centre" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="centre" vertical="centre"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="centre" vertical="centre"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="centre" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="centre"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="centre" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="centre" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="centre"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="centre" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="centre" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="centre"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="centre" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="centre"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="centre" vertical="centre"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="centre" vertical="centre"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="centre" vertical="centre" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="centre" vertical="centre"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="centre" vertical="centre"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="centre" vertical="centre" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="centre" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="15" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="centre" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="centre" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="centre" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="centre" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="centre" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="centre" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="centre" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="centre" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="19" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="centre" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="centre" vertical="centre"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="centre" vertical="centre" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="centre" vertical="centre"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="centre" vertical="centre" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="15" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="centre" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="centre" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="centre" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="centre" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="19" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="centre" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="centre" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -696,89 +1120,148 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="14" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="78" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="12" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="72" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="12" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="12" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="12" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="12" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="12" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="12" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1">
-      <x:c r="A1" s="5" t="str">
-        <x:v>Artificial Intelligence and Healthcare Economics — Core Resource Workbooks</x:v>
-      </x:c>
-      <x:c r="B1" s="5"/>
-      <x:c r="C1" s="5"/>
-      <x:c r="D1" s="5"/>
-      <x:c r="E1" s="5"/>
-      <x:c r="F1" s="5"/>
-      <x:c r="G1" s="5"/>
-      <x:c r="H1" s="5"/>
-    </x:row>
-    <x:row r="3">
-      <x:c r="A3" s="16" t="str">
-        <x:v>Release</x:v>
-      </x:c>
-      <x:c r="B3" s="17" t="str">
-        <x:v>V1.0</x:v>
-      </x:c>
+    <x:row r="1" ht="42" customHeight="1">
+      <x:c r="A1" s="92" t="str">
+        <x:v>Artificial Intelligence and Healthcare Economics</x:v>
+      </x:c>
+      <x:c r="B1" s="92"/>
+      <x:c r="C1" s="93"/>
+      <x:c r="D1" s="93"/>
+      <x:c r="E1" s="93"/>
+      <x:c r="F1" s="93"/>
+      <x:c r="G1" s="93"/>
+      <x:c r="H1" s="93"/>
+    </x:row>
+    <x:row r="2" ht="24" customHeight="1">
+      <x:c r="A2" s="113" t="str">
+        <x:v>Evidence, Value, Governance, and Sustainability</x:v>
+      </x:c>
+      <x:c r="B2" s="113"/>
+      <x:c r="C2" s="94"/>
+      <x:c r="D2" s="94"/>
+      <x:c r="E2" s="94"/>
+      <x:c r="F2" s="94"/>
+      <x:c r="G2" s="94"/>
+      <x:c r="H2" s="94"/>
+    </x:row>
+    <x:row r="3" ht="34" customHeight="1">
+      <x:c r="A3" s="134" t="str">
+        <x:v>Digital Resource Companion — Consolidated Core Resource Workbooks</x:v>
+      </x:c>
+      <x:c r="B3" s="134"/>
+      <x:c r="C3" s="96"/>
+      <x:c r="D3" s="96"/>
+      <x:c r="E3" s="96"/>
+      <x:c r="F3" s="96"/>
+      <x:c r="G3" s="96"/>
+      <x:c r="H3" s="96"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="16" t="str">
-        <x:v>Scope</x:v>
-      </x:c>
-      <x:c r="B4" s="17" t="str">
-        <x:v>All 24 canonical core institutional records in the current five-Part, fifteen-chapter structure.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5">
-      <x:c r="A5" s="16" t="str">
+      <x:c r="A4" s="118" t="str">
+        <x:v>Muthana Zouri · Carmen Marinela Cumpăt</x:v>
+      </x:c>
+      <x:c r="B4" s="119"/>
+      <x:c r="C4" s="99"/>
+      <x:c r="D4" s="99"/>
+      <x:c r="E4" s="99"/>
+      <x:c r="F4" s="99"/>
+      <x:c r="G4" s="99"/>
+      <x:c r="H4" s="99"/>
+    </x:row>
+    <x:row r="5" ht="30" customHeight="1">
+      <x:c r="A5" s="132" t="str">
+        <x:v>Grigore T. Popa University of Medicine and Pharmacy Publishing House · V1.0 · 2026</x:v>
+      </x:c>
+      <x:c r="B5" s="133"/>
+      <x:c r="C5" s="102"/>
+      <x:c r="D5" s="102"/>
+      <x:c r="E5" s="102"/>
+      <x:c r="F5" s="102"/>
+      <x:c r="G5" s="102"/>
+      <x:c r="H5" s="102"/>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="16"/>
+      <x:c r="B6" s="17"/>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="124" t="str">
+        <x:v>How to use this workbook</x:v>
+      </x:c>
+      <x:c r="B7" s="124"/>
+      <x:c r="C7" s="104"/>
+      <x:c r="D7" s="104"/>
+      <x:c r="E7" s="104"/>
+      <x:c r="F7" s="104"/>
+      <x:c r="G7" s="104"/>
+      <x:c r="H7" s="104"/>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="105" t="str">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="B5" s="17" t="str">
+      <x:c r="B8" s="107" t="str">
         <x:v>Begin with the institutional decision and realistic comparator, not with the worksheet.</x:v>
       </x:c>
     </x:row>
-    <x:row r="6">
-      <x:c r="A6" s="16" t="str">
+    <x:row r="9">
+      <x:c r="A9" s="105" t="str">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="B6" s="17" t="str">
+      <x:c r="B9" s="107" t="str">
         <x:v>Select only the records proportionate to consequence, uncertainty, scale, and institutional dependence.</x:v>
       </x:c>
     </x:row>
-    <x:row r="7">
-      <x:c r="A7" s="16" t="str">
+    <x:row r="10">
+      <x:c r="A10" s="105" t="str">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="B7" s="17" t="str">
+      <x:c r="B10" s="107" t="str">
         <x:v>Create a governed local copy and retain the resource ID, release, owner, evidence cut-off, and modification date.</x:v>
       </x:c>
     </x:row>
-    <x:row r="8">
-      <x:c r="A8" s="16" t="str">
+    <x:row r="11">
+      <x:c r="A11" s="106" t="str">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="B8" s="17" t="str">
+      <x:c r="B11" s="107" t="str">
         <x:v>Replace generic or synthetic material with authorized, versioned local evidence; mark unknowns explicitly.</x:v>
       </x:c>
     </x:row>
-    <x:row r="9">
-      <x:c r="A9" s="16" t="str">
+    <x:row r="12">
+      <x:c r="A12" s="106" t="str">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="B9" s="17" t="str">
+      <x:c r="B12" s="107" t="str">
         <x:v>Do not enter identifiable patient information, credentials, private keys, confidential contracts, or uncontrolled data.</x:v>
       </x:c>
     </x:row>
-    <x:row r="10">
-      <x:c r="A10" s="16" t="str">
+    <x:row r="13">
+      <x:c r="A13" s="106" t="str">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="B10" s="17" t="str">
-        <x:v>End with a decision, conditions, monitoring thresholds, review date, trigger events, and exit route.</x:v>
+      <x:c r="B13" s="107" t="str">
+        <x:v>End with a decision, conditions, monitoring thresholds, review date, trigger events, and an exit route.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A1:H1"/>
+    <x:mergeCell ref="A1:B1"/>
+    <x:mergeCell ref="A2:B2"/>
+    <x:mergeCell ref="A3:B3"/>
+    <x:mergeCell ref="A4:B4"/>
+    <x:mergeCell ref="A5:B5"/>
+    <x:mergeCell ref="A7:B7"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -794,23 +1277,29 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="29" t="str">
+      <x:c r="A1" s="78" t="str">
         <x:v>AIHE-C02 — Corrective and Preventive Action Record</x:v>
       </x:c>
-      <x:c r="B1" s="29"/>
-      <x:c r="C1" s="29"/>
-      <x:c r="D1" s="29"/>
+      <x:c r="B1" s="78"/>
+      <x:c r="C1" s="78"/>
+      <x:c r="D1" s="78"/>
       <x:c r="E1" s="29"/>
       <x:c r="F1" s="29"/>
     </x:row>
+    <x:row r="2">
+      <x:c r="A2"/>
+      <x:c r="B2"/>
+      <x:c r="C2"/>
+      <x:c r="D2"/>
+    </x:row>
     <x:row r="3">
-      <x:c r="A3" s="33" t="str">
+      <x:c r="A3" s="80" t="str">
         <x:v>Primary chapter</x:v>
       </x:c>
       <x:c r="B3" s="17" t="str">
         <x:v>5 — Quality, Accreditation, and Organizational Learning</x:v>
       </x:c>
-      <x:c r="C3" s="33" t="str">
+      <x:c r="C3" s="80" t="str">
         <x:v>Release</x:v>
       </x:c>
       <x:c r="D3" s="17" t="str">
@@ -818,13 +1307,13 @@
       </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="33" t="str">
+      <x:c r="A4" s="80" t="str">
         <x:v>Purpose</x:v>
       </x:c>
       <x:c r="B4" s="17" t="str">
         <x:v>Document nonconformity, containment, causal analysis, corrective and preventive action, effectiveness, residual risk, and closure.</x:v>
       </x:c>
-      <x:c r="C4" s="33" t="str">
+      <x:c r="C4" s="80" t="str">
         <x:v>Reader level</x:v>
       </x:c>
       <x:c r="D4" s="17" t="str">
@@ -832,13 +1321,13 @@
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="33" t="str">
+      <x:c r="A5" s="80" t="str">
         <x:v>Required inputs</x:v>
       </x:c>
       <x:c r="B5" s="17" t="str">
         <x:v>Defined decision problem, realistic comparator, local evidence, named owners, and applicable institutional requirements</x:v>
       </x:c>
-      <x:c r="C5" s="33" t="str">
+      <x:c r="C5" s="80" t="str">
         <x:v>Expected output</x:v>
       </x:c>
       <x:c r="D5" s="17" t="str">
@@ -859,6 +1348,12 @@
         <x:v>60–180 minutes</x:v>
       </x:c>
     </x:row>
+    <x:row r="7">
+      <x:c r="A7"/>
+      <x:c r="B7"/>
+      <x:c r="C7"/>
+      <x:c r="D7"/>
+    </x:row>
     <x:row r="8">
       <x:c r="A8" s="23" t="str">
         <x:v>Field</x:v>
@@ -869,6 +1364,7 @@
       <x:c r="C8" s="23" t="str">
         <x:v>Institutional response</x:v>
       </x:c>
+      <x:c r="D8"/>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="17" t="str">
@@ -877,7 +1373,8 @@
       <x:c r="B9" s="17" t="str">
         <x:v>Describe the indicator, incident, complaint, audit finding, accreditation gap, or threshold breach.</x:v>
       </x:c>
-      <x:c r="C9" s="17" t="str"/>
+      <x:c r="C9" s="17"/>
+      <x:c r="D9"/>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="17" t="str">
@@ -886,7 +1383,8 @@
       <x:c r="B10" s="17" t="str">
         <x:v>Record patient, workforce, data, service, and continuity protections, including restriction or pause.</x:v>
       </x:c>
-      <x:c r="C10" s="17" t="str"/>
+      <x:c r="C10" s="17"/>
+      <x:c r="D10"/>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="17" t="str">
@@ -895,7 +1393,8 @@
       <x:c r="B11" s="17" t="str">
         <x:v>Preserve data state, model and software version, output, human action, timing, workload, and context.</x:v>
       </x:c>
-      <x:c r="C11" s="17" t="str"/>
+      <x:c r="C11" s="17"/>
+      <x:c r="D11"/>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="17" t="str">
@@ -904,7 +1403,8 @@
       <x:c r="B12" s="17" t="str">
         <x:v>Identify confirmed and competing technical, clinical, workflow, organizational, and governance causes.</x:v>
       </x:c>
-      <x:c r="C12" s="17" t="str"/>
+      <x:c r="C12" s="17"/>
+      <x:c r="D12"/>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="17" t="str">
@@ -913,7 +1413,8 @@
       <x:c r="B13" s="17" t="str">
         <x:v>Define action, responsible owner, due date, revalidation, communication, and contract or vendor response.</x:v>
       </x:c>
-      <x:c r="C13" s="17" t="str"/>
+      <x:c r="C13" s="17"/>
+      <x:c r="D13"/>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="17" t="str">
@@ -922,7 +1423,8 @@
       <x:c r="B14" s="17" t="str">
         <x:v>Identify controls intended to prevent recurrence in this and related systems.</x:v>
       </x:c>
-      <x:c r="C14" s="17" t="str"/>
+      <x:c r="C14" s="17"/>
+      <x:c r="D14"/>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="17" t="str">
@@ -931,7 +1433,8 @@
       <x:c r="B15" s="17" t="str">
         <x:v>Define evidence, observation period, threshold, independent review, and residual uncertainty.</x:v>
       </x:c>
-      <x:c r="C15" s="17" t="str"/>
+      <x:c r="C15" s="17"/>
+      <x:c r="D15"/>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="17" t="str">
@@ -940,15 +1443,17 @@
       <x:c r="B16" s="17" t="str">
         <x:v>Record decision, date, dissent, residual risk, and next review.</x:v>
       </x:c>
-      <x:c r="C16" s="17" t="str"/>
+      <x:c r="C16" s="17"/>
+      <x:c r="D16"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:F1"/>
+    <x:mergeCell ref="A1:D1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rec86bee2db444fe9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5c4372bd3f1b42cd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -963,23 +1468,29 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="29" t="str">
+      <x:c r="A1" s="78" t="str">
         <x:v>AIHE-B01 — Economic Evaluation Specification</x:v>
       </x:c>
-      <x:c r="B1" s="29"/>
-      <x:c r="C1" s="29"/>
-      <x:c r="D1" s="29"/>
+      <x:c r="B1" s="78"/>
+      <x:c r="C1" s="78"/>
+      <x:c r="D1" s="78"/>
       <x:c r="E1" s="29"/>
       <x:c r="F1" s="29"/>
     </x:row>
+    <x:row r="2">
+      <x:c r="A2"/>
+      <x:c r="B2"/>
+      <x:c r="C2"/>
+      <x:c r="D2"/>
+    </x:row>
     <x:row r="3">
-      <x:c r="A3" s="33" t="str">
+      <x:c r="A3" s="80" t="str">
         <x:v>Primary chapter</x:v>
       </x:c>
       <x:c r="B3" s="17" t="str">
         <x:v>6 — Lifecycle Cost, Pricing, and Benefit Realization</x:v>
       </x:c>
-      <x:c r="C3" s="33" t="str">
+      <x:c r="C3" s="80" t="str">
         <x:v>Release</x:v>
       </x:c>
       <x:c r="D3" s="17" t="str">
@@ -987,13 +1498,13 @@
       </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="33" t="str">
+      <x:c r="A4" s="80" t="str">
         <x:v>Purpose</x:v>
       </x:c>
       <x:c r="B4" s="17" t="str">
         <x:v>Define the economic decision, perspective, comparator, horizon, outcomes, costs, methods, uncertainty, safeguards, and validation.</x:v>
       </x:c>
-      <x:c r="C4" s="33" t="str">
+      <x:c r="C4" s="80" t="str">
         <x:v>Reader level</x:v>
       </x:c>
       <x:c r="D4" s="17" t="str">
@@ -1001,13 +1512,13 @@
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="33" t="str">
+      <x:c r="A5" s="80" t="str">
         <x:v>Required inputs</x:v>
       </x:c>
       <x:c r="B5" s="17" t="str">
         <x:v>Defined decision problem, realistic comparator, local evidence, named owners, and applicable institutional requirements</x:v>
       </x:c>
-      <x:c r="C5" s="33" t="str">
+      <x:c r="C5" s="80" t="str">
         <x:v>Expected output</x:v>
       </x:c>
       <x:c r="D5" s="17" t="str">
@@ -1028,6 +1539,12 @@
         <x:v>60–180 minutes</x:v>
       </x:c>
     </x:row>
+    <x:row r="7">
+      <x:c r="A7"/>
+      <x:c r="B7"/>
+      <x:c r="C7"/>
+      <x:c r="D7"/>
+    </x:row>
     <x:row r="8">
       <x:c r="A8" s="23" t="str">
         <x:v>Field</x:v>
@@ -1038,6 +1555,7 @@
       <x:c r="C8" s="23" t="str">
         <x:v>Institutional response</x:v>
       </x:c>
+      <x:c r="D8"/>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="17" t="str">
@@ -1046,7 +1564,8 @@
       <x:c r="B9" s="17" t="str">
         <x:v>State the incremental decision and all realistic alternatives.</x:v>
       </x:c>
-      <x:c r="C9" s="17" t="str"/>
+      <x:c r="C9" s="17"/>
+      <x:c r="D9"/>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="17" t="str">
@@ -1055,7 +1574,8 @@
       <x:c r="B10" s="17" t="str">
         <x:v>Define eligible volume, uptake, important heterogeneity, and access constraints.</x:v>
       </x:c>
-      <x:c r="C10" s="17" t="str"/>
+      <x:c r="C10" s="17"/>
+      <x:c r="D10"/>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="17" t="str">
@@ -1064,7 +1584,8 @@
       <x:c r="B11" s="17" t="str">
         <x:v>Distinguish hospital, payer, patient, societal, and environmental perspectives and identify who pays and benefits.</x:v>
       </x:c>
-      <x:c r="C11" s="17" t="str"/>
+      <x:c r="C11" s="17"/>
+      <x:c r="D11"/>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="17" t="str">
@@ -1073,7 +1594,8 @@
       <x:c r="B12" s="17" t="str">
         <x:v>Justify duration, timing of implementation, useful life, updating, residual value, and discount rates.</x:v>
       </x:c>
-      <x:c r="C12" s="17" t="str"/>
+      <x:c r="C12" s="17"/>
+      <x:c r="D12"/>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="17" t="str">
@@ -1082,7 +1604,8 @@
       <x:c r="B13" s="17" t="str">
         <x:v>Separate final health outcomes, intermediate outcomes, process measures, workforce effects, quality, equity, trust, and environmental effects.</x:v>
       </x:c>
-      <x:c r="C13" s="17" t="str"/>
+      <x:c r="C13" s="17"/>
+      <x:c r="D13"/>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="17" t="str">
@@ -1091,7 +1614,8 @@
       <x:c r="B14" s="17" t="str">
         <x:v>Include acquisition, data, integration, infrastructure, training, review, governance, monitoring, incidents, updates, support, opportunity cost, and exit where incremental.</x:v>
       </x:c>
-      <x:c r="C14" s="17" t="str"/>
+      <x:c r="C14" s="17"/>
+      <x:c r="D14"/>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="17" t="str">
@@ -1100,7 +1624,8 @@
       <x:c r="B15" s="17" t="str">
         <x:v>Specify cost-consequence, cost-effectiveness, cost-utility, cost-benefit, budget impact, ROI, multi-criteria, or combined analysis.</x:v>
       </x:c>
-      <x:c r="C15" s="17" t="str"/>
+      <x:c r="C15" s="17"/>
+      <x:c r="D15"/>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="17" t="str">
@@ -1109,7 +1634,8 @@
       <x:c r="B16" s="17" t="str">
         <x:v>Define deterministic, probabilistic, scenario, threshold, structural, subgroup, and value-of-information analyses.</x:v>
       </x:c>
-      <x:c r="C16" s="17" t="str"/>
+      <x:c r="C16" s="17"/>
+      <x:c r="D16"/>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="17" t="str">
@@ -1118,7 +1644,8 @@
       <x:c r="B17" s="17" t="str">
         <x:v>State willingness-to-pay or net-benefit rule, affordability threshold, mandatory safeguards, and conditions.</x:v>
       </x:c>
-      <x:c r="C17" s="17" t="str"/>
+      <x:c r="C17" s="17"/>
+      <x:c r="D17"/>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="17" t="str">
@@ -1127,15 +1654,17 @@
       <x:c r="B18" s="17" t="str">
         <x:v>Record model version, evidence date, technical verification, face validity, external review, reproducibility, and archive location.</x:v>
       </x:c>
-      <x:c r="C18" s="17" t="str"/>
+      <x:c r="C18" s="17"/>
+      <x:c r="D18"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:F1"/>
+    <x:mergeCell ref="A1:D1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R81435dc90ad74f91"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R072fb287267345ec"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1156,59 +1685,85 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="29" t="str">
+      <x:c r="A1" s="78" t="str">
         <x:v>AIHE-B02 — Lifecycle Cost and Pricing Record</x:v>
       </x:c>
-      <x:c r="B1" s="29"/>
-      <x:c r="C1" s="29"/>
-      <x:c r="D1" s="29"/>
-      <x:c r="E1" s="29"/>
-      <x:c r="F1" s="29"/>
-      <x:c r="G1" s="29"/>
-      <x:c r="H1" s="29"/>
-      <x:c r="I1" s="29"/>
+      <x:c r="B1" s="78"/>
+      <x:c r="C1" s="78"/>
+      <x:c r="D1" s="78"/>
+      <x:c r="E1" s="78"/>
+      <x:c r="F1" s="78"/>
+      <x:c r="G1" s="78"/>
+      <x:c r="H1" s="78"/>
+      <x:c r="I1" s="78"/>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2"/>
+      <x:c r="B2"/>
+      <x:c r="C2"/>
+      <x:c r="D2"/>
+      <x:c r="E2"/>
+      <x:c r="F2"/>
+      <x:c r="G2"/>
+      <x:c r="H2"/>
+      <x:c r="I2"/>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="33" t="str">
+      <x:c r="A3" s="80" t="str">
         <x:v>Primary chapter</x:v>
       </x:c>
       <x:c r="B3" s="17" t="str">
         <x:v>6 — Lifecycle Cost, Pricing, and Benefit Realization</x:v>
       </x:c>
-      <x:c r="C3" s="33" t="str">
+      <x:c r="C3" s="80" t="str">
         <x:v>Release</x:v>
       </x:c>
       <x:c r="D3" s="17" t="str">
         <x:v>V1.0</x:v>
       </x:c>
+      <x:c r="E3"/>
+      <x:c r="F3"/>
+      <x:c r="G3"/>
+      <x:c r="H3"/>
+      <x:c r="I3"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="33" t="str">
+      <x:c r="A4" s="80" t="str">
         <x:v>Purpose</x:v>
       </x:c>
       <x:c r="B4" s="17" t="str">
         <x:v>Record acquisition through exit costs, resource use, pricing exposure, opportunity cost, residual value, and evidence.</x:v>
       </x:c>
-      <x:c r="C4" s="33" t="str">
+      <x:c r="C4" s="80" t="str">
         <x:v>Reader level</x:v>
       </x:c>
       <x:c r="D4" s="17" t="str">
         <x:v>Applied</x:v>
       </x:c>
+      <x:c r="E4"/>
+      <x:c r="F4"/>
+      <x:c r="G4"/>
+      <x:c r="H4"/>
+      <x:c r="I4"/>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="33" t="str">
+      <x:c r="A5" s="80" t="str">
         <x:v>Required inputs</x:v>
       </x:c>
       <x:c r="B5" s="17" t="str">
         <x:v>Defined decision problem, realistic comparator, local evidence, named owners, and applicable institutional requirements</x:v>
       </x:c>
-      <x:c r="C5" s="33" t="str">
+      <x:c r="C5" s="80" t="str">
         <x:v>Expected output</x:v>
       </x:c>
       <x:c r="D5" s="17" t="str">
         <x:v>Versioned institutional decision record with conditions, monitoring, review date, and exit route</x:v>
       </x:c>
+      <x:c r="E5"/>
+      <x:c r="F5"/>
+      <x:c r="G5"/>
+      <x:c r="H5"/>
+      <x:c r="I5"/>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="33" t="str">
@@ -1223,6 +1778,22 @@
       <x:c r="D6" s="17" t="str">
         <x:v>60–180 minutes</x:v>
       </x:c>
+      <x:c r="E6"/>
+      <x:c r="F6"/>
+      <x:c r="G6"/>
+      <x:c r="H6"/>
+      <x:c r="I6"/>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7"/>
+      <x:c r="B7"/>
+      <x:c r="C7"/>
+      <x:c r="D7"/>
+      <x:c r="E7"/>
+      <x:c r="F7"/>
+      <x:c r="G7"/>
+      <x:c r="H7"/>
+      <x:c r="I7"/>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="23" t="str">
@@ -1257,144 +1828,144 @@
       <x:c r="A9" s="17" t="str">
         <x:v>Acquisition and licence</x:v>
       </x:c>
-      <x:c r="B9" s="17" t="str"/>
-      <x:c r="C9" s="17" t="str"/>
-      <x:c r="D9" s="17" t="str"/>
-      <x:c r="E9" s="17" t="str"/>
-      <x:c r="F9" s="17" t="str"/>
-      <x:c r="G9" s="17" t="str"/>
-      <x:c r="H9" s="17" t="str"/>
-      <x:c r="I9" s="17" t="str"/>
+      <x:c r="B9" s="17"/>
+      <x:c r="C9" s="17"/>
+      <x:c r="D9" s="17"/>
+      <x:c r="E9" s="17"/>
+      <x:c r="F9" s="17"/>
+      <x:c r="G9" s="17"/>
+      <x:c r="H9" s="17"/>
+      <x:c r="I9" s="17"/>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="17" t="str">
         <x:v>Data preparation and governance</x:v>
       </x:c>
-      <x:c r="B10" s="17" t="str"/>
-      <x:c r="C10" s="17" t="str"/>
-      <x:c r="D10" s="17" t="str"/>
-      <x:c r="E10" s="17" t="str"/>
-      <x:c r="F10" s="17" t="str"/>
-      <x:c r="G10" s="17" t="str"/>
-      <x:c r="H10" s="17" t="str"/>
-      <x:c r="I10" s="17" t="str"/>
+      <x:c r="B10" s="17"/>
+      <x:c r="C10" s="17"/>
+      <x:c r="D10" s="17"/>
+      <x:c r="E10" s="17"/>
+      <x:c r="F10" s="17"/>
+      <x:c r="G10" s="17"/>
+      <x:c r="H10" s="17"/>
+      <x:c r="I10" s="17"/>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="17" t="str">
         <x:v>Integration and infrastructure</x:v>
       </x:c>
-      <x:c r="B11" s="17" t="str"/>
-      <x:c r="C11" s="17" t="str"/>
-      <x:c r="D11" s="17" t="str"/>
-      <x:c r="E11" s="17" t="str"/>
-      <x:c r="F11" s="17" t="str"/>
-      <x:c r="G11" s="17" t="str"/>
-      <x:c r="H11" s="17" t="str"/>
-      <x:c r="I11" s="17" t="str"/>
+      <x:c r="B11" s="17"/>
+      <x:c r="C11" s="17"/>
+      <x:c r="D11" s="17"/>
+      <x:c r="E11" s="17"/>
+      <x:c r="F11" s="17"/>
+      <x:c r="G11" s="17"/>
+      <x:c r="H11" s="17"/>
+      <x:c r="I11" s="17"/>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="17" t="str">
         <x:v>Validation and assurance</x:v>
       </x:c>
-      <x:c r="B12" s="17" t="str"/>
-      <x:c r="C12" s="17" t="str"/>
-      <x:c r="D12" s="17" t="str"/>
-      <x:c r="E12" s="17" t="str"/>
-      <x:c r="F12" s="17" t="str"/>
-      <x:c r="G12" s="17" t="str"/>
-      <x:c r="H12" s="17" t="str"/>
-      <x:c r="I12" s="17" t="str"/>
+      <x:c r="B12" s="17"/>
+      <x:c r="C12" s="17"/>
+      <x:c r="D12" s="17"/>
+      <x:c r="E12" s="17"/>
+      <x:c r="F12" s="17"/>
+      <x:c r="G12" s="17"/>
+      <x:c r="H12" s="17"/>
+      <x:c r="I12" s="17"/>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="17" t="str">
         <x:v>Training, workflow, and review</x:v>
       </x:c>
-      <x:c r="B13" s="17" t="str"/>
-      <x:c r="C13" s="17" t="str"/>
-      <x:c r="D13" s="17" t="str"/>
-      <x:c r="E13" s="17" t="str"/>
-      <x:c r="F13" s="17" t="str"/>
-      <x:c r="G13" s="17" t="str"/>
-      <x:c r="H13" s="17" t="str"/>
-      <x:c r="I13" s="17" t="str"/>
+      <x:c r="B13" s="17"/>
+      <x:c r="C13" s="17"/>
+      <x:c r="D13" s="17"/>
+      <x:c r="E13" s="17"/>
+      <x:c r="F13" s="17"/>
+      <x:c r="G13" s="17"/>
+      <x:c r="H13" s="17"/>
+      <x:c r="I13" s="17"/>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="17" t="str">
         <x:v>Quality, ethics, legal, and audit</x:v>
       </x:c>
-      <x:c r="B14" s="17" t="str"/>
-      <x:c r="C14" s="17" t="str"/>
-      <x:c r="D14" s="17" t="str"/>
-      <x:c r="E14" s="17" t="str"/>
-      <x:c r="F14" s="17" t="str"/>
-      <x:c r="G14" s="17" t="str"/>
-      <x:c r="H14" s="17" t="str"/>
-      <x:c r="I14" s="17" t="str"/>
+      <x:c r="B14" s="17"/>
+      <x:c r="C14" s="17"/>
+      <x:c r="D14" s="17"/>
+      <x:c r="E14" s="17"/>
+      <x:c r="F14" s="17"/>
+      <x:c r="G14" s="17"/>
+      <x:c r="H14" s="17"/>
+      <x:c r="I14" s="17"/>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="17" t="str">
         <x:v>Cybersecurity, resilience, and incidents</x:v>
       </x:c>
-      <x:c r="B15" s="17" t="str"/>
-      <x:c r="C15" s="17" t="str"/>
-      <x:c r="D15" s="17" t="str"/>
-      <x:c r="E15" s="17" t="str"/>
-      <x:c r="F15" s="17" t="str"/>
-      <x:c r="G15" s="17" t="str"/>
-      <x:c r="H15" s="17" t="str"/>
-      <x:c r="I15" s="17" t="str"/>
+      <x:c r="B15" s="17"/>
+      <x:c r="C15" s="17"/>
+      <x:c r="D15" s="17"/>
+      <x:c r="E15" s="17"/>
+      <x:c r="F15" s="17"/>
+      <x:c r="G15" s="17"/>
+      <x:c r="H15" s="17"/>
+      <x:c r="I15" s="17"/>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="17" t="str">
         <x:v>Monitoring, updating, and support</x:v>
       </x:c>
-      <x:c r="B16" s="17" t="str"/>
-      <x:c r="C16" s="17" t="str"/>
-      <x:c r="D16" s="17" t="str"/>
-      <x:c r="E16" s="17" t="str"/>
-      <x:c r="F16" s="17" t="str"/>
-      <x:c r="G16" s="17" t="str"/>
-      <x:c r="H16" s="17" t="str"/>
-      <x:c r="I16" s="17" t="str"/>
+      <x:c r="B16" s="17"/>
+      <x:c r="C16" s="17"/>
+      <x:c r="D16" s="17"/>
+      <x:c r="E16" s="17"/>
+      <x:c r="F16" s="17"/>
+      <x:c r="G16" s="17"/>
+      <x:c r="H16" s="17"/>
+      <x:c r="I16" s="17"/>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="17" t="str">
         <x:v>Opportunity cost and displaced capacity</x:v>
       </x:c>
-      <x:c r="B17" s="17" t="str"/>
-      <x:c r="C17" s="17" t="str"/>
-      <x:c r="D17" s="17" t="str"/>
-      <x:c r="E17" s="17" t="str"/>
-      <x:c r="F17" s="17" t="str"/>
-      <x:c r="G17" s="17" t="str"/>
-      <x:c r="H17" s="17" t="str"/>
-      <x:c r="I17" s="17" t="str"/>
+      <x:c r="B17" s="17"/>
+      <x:c r="C17" s="17"/>
+      <x:c r="D17" s="17"/>
+      <x:c r="E17" s="17"/>
+      <x:c r="F17" s="17"/>
+      <x:c r="G17" s="17"/>
+      <x:c r="H17" s="17"/>
+      <x:c r="I17" s="17"/>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="17" t="str">
         <x:v>Exit, transition, and decommissioning</x:v>
       </x:c>
-      <x:c r="B18" s="17" t="str"/>
-      <x:c r="C18" s="17" t="str"/>
-      <x:c r="D18" s="17" t="str"/>
-      <x:c r="E18" s="17" t="str"/>
-      <x:c r="F18" s="17" t="str"/>
-      <x:c r="G18" s="17" t="str"/>
-      <x:c r="H18" s="17" t="str"/>
-      <x:c r="I18" s="17" t="str"/>
+      <x:c r="B18" s="17"/>
+      <x:c r="C18" s="17"/>
+      <x:c r="D18" s="17"/>
+      <x:c r="E18" s="17"/>
+      <x:c r="F18" s="17"/>
+      <x:c r="G18" s="17"/>
+      <x:c r="H18" s="17"/>
+      <x:c r="I18" s="17"/>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="17" t="str">
         <x:v>Residual value or recovery credit</x:v>
       </x:c>
-      <x:c r="B19" s="17" t="str"/>
-      <x:c r="C19" s="17" t="str"/>
-      <x:c r="D19" s="17" t="str"/>
-      <x:c r="E19" s="17" t="str"/>
-      <x:c r="F19" s="17" t="str"/>
-      <x:c r="G19" s="17" t="str"/>
-      <x:c r="H19" s="17" t="str"/>
-      <x:c r="I19" s="17" t="str"/>
+      <x:c r="B19" s="17"/>
+      <x:c r="C19" s="17"/>
+      <x:c r="D19" s="17"/>
+      <x:c r="E19" s="17"/>
+      <x:c r="F19" s="17"/>
+      <x:c r="G19" s="17"/>
+      <x:c r="H19" s="17"/>
+      <x:c r="I19" s="17"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -1402,7 +1973,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1fd4a0a9d73346bf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1d0e2e13448e45a2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1417,23 +1988,29 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="29" t="str">
+      <x:c r="A1" s="78" t="str">
         <x:v>AIHE-B04 — Cost-Effectiveness, Budget Impact, and HTA Record</x:v>
       </x:c>
-      <x:c r="B1" s="29"/>
-      <x:c r="C1" s="29"/>
-      <x:c r="D1" s="29"/>
+      <x:c r="B1" s="78"/>
+      <x:c r="C1" s="78"/>
+      <x:c r="D1" s="78"/>
       <x:c r="E1" s="29"/>
       <x:c r="F1" s="29"/>
     </x:row>
+    <x:row r="2">
+      <x:c r="A2"/>
+      <x:c r="B2"/>
+      <x:c r="C2"/>
+      <x:c r="D2"/>
+    </x:row>
     <x:row r="3">
-      <x:c r="A3" s="33" t="str">
+      <x:c r="A3" s="80" t="str">
         <x:v>Primary chapter</x:v>
       </x:c>
       <x:c r="B3" s="17" t="str">
         <x:v>7 — Economic Evaluation, Affordability, and HTA</x:v>
       </x:c>
-      <x:c r="C3" s="33" t="str">
+      <x:c r="C3" s="80" t="str">
         <x:v>Release</x:v>
       </x:c>
       <x:c r="D3" s="17" t="str">
@@ -1441,13 +2018,13 @@
       </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="33" t="str">
+      <x:c r="A4" s="80" t="str">
         <x:v>Purpose</x:v>
       </x:c>
       <x:c r="B4" s="17" t="str">
         <x:v>Summarize cost-effectiveness, affordability, distribution, HTA, reimbursement, adoption conditions, uncertainty, and recommendation.</x:v>
       </x:c>
-      <x:c r="C4" s="33" t="str">
+      <x:c r="C4" s="80" t="str">
         <x:v>Reader level</x:v>
       </x:c>
       <x:c r="D4" s="17" t="str">
@@ -1455,13 +2032,13 @@
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="33" t="str">
+      <x:c r="A5" s="80" t="str">
         <x:v>Required inputs</x:v>
       </x:c>
       <x:c r="B5" s="17" t="str">
         <x:v>Defined decision problem, realistic comparator, local evidence, named owners, and applicable institutional requirements</x:v>
       </x:c>
-      <x:c r="C5" s="33" t="str">
+      <x:c r="C5" s="80" t="str">
         <x:v>Expected output</x:v>
       </x:c>
       <x:c r="D5" s="17" t="str">
@@ -1482,6 +2059,12 @@
         <x:v>60–180 minutes</x:v>
       </x:c>
     </x:row>
+    <x:row r="7">
+      <x:c r="A7"/>
+      <x:c r="B7"/>
+      <x:c r="C7"/>
+      <x:c r="D7"/>
+    </x:row>
     <x:row r="8">
       <x:c r="A8" s="23" t="str">
         <x:v>Field</x:v>
@@ -1492,6 +2075,7 @@
       <x:c r="C8" s="23" t="str">
         <x:v>Institutional response</x:v>
       </x:c>
+      <x:c r="D8"/>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="17" t="str">
@@ -1500,7 +2084,8 @@
       <x:c r="B9" s="17" t="str">
         <x:v>Report disaggregated and summary results relative to the comparator.</x:v>
       </x:c>
-      <x:c r="C9" s="17" t="str"/>
+      <x:c r="C9" s="17"/>
+      <x:c r="D9"/>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="17" t="str">
@@ -1509,7 +2094,8 @@
       <x:c r="B10" s="17" t="str">
         <x:v>State the threshold, currency and price year, and probability that the preferred option is cost-effective.</x:v>
       </x:c>
-      <x:c r="C10" s="17" t="str"/>
+      <x:c r="C10" s="17"/>
+      <x:c r="D10"/>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="17" t="str">
@@ -1518,7 +2104,8 @@
       <x:c r="B11" s="17" t="str">
         <x:v>Report eligible volume, uptake, implementation timing, annual cash flow, funding source, and cashable versus non-cashable savings.</x:v>
       </x:c>
-      <x:c r="C11" s="17" t="str"/>
+      <x:c r="C11" s="17"/>
+      <x:c r="D11"/>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="17" t="str">
@@ -1527,7 +2114,8 @@
       <x:c r="B12" s="17" t="str">
         <x:v>Report subgroup outcomes, access, burdens, opportunity costs, mitigation, and residual concern.</x:v>
       </x:c>
-      <x:c r="C12" s="17" t="str"/>
+      <x:c r="C12" s="17"/>
+      <x:c r="D12"/>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="17" t="str">
@@ -1536,7 +2124,8 @@
       <x:c r="B13" s="17" t="str">
         <x:v>Distinguish authorization, external clinical evidence, joint or national assessment, and local evidence.</x:v>
       </x:c>
-      <x:c r="C13" s="17" t="str"/>
+      <x:c r="C13" s="17"/>
+      <x:c r="D13"/>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="17" t="str">
@@ -1545,7 +2134,8 @@
       <x:c r="B14" s="17" t="str">
         <x:v>Identify coverage, coding, tariff, payer, claim, denial, and incentive implications.</x:v>
       </x:c>
-      <x:c r="C14" s="17" t="str"/>
+      <x:c r="C14" s="17"/>
+      <x:c r="D14"/>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="17" t="str">
@@ -1554,7 +2144,8 @@
       <x:c r="B15" s="17" t="str">
         <x:v>Record readiness, procurement, workforce, quality, accreditation, governance, and monitoring prerequisites.</x:v>
       </x:c>
-      <x:c r="C15" s="17" t="str"/>
+      <x:c r="C15" s="17"/>
+      <x:c r="D15"/>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="17" t="str">
@@ -1563,7 +2154,8 @@
       <x:c r="B16" s="17" t="str">
         <x:v>Identify parameters that may change the decision and the value, cost, and timing of further research.</x:v>
       </x:c>
-      <x:c r="C16" s="17" t="str"/>
+      <x:c r="C16" s="17"/>
+      <x:c r="D16"/>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="17" t="str">
@@ -1572,15 +2164,17 @@
       <x:c r="B17" s="17" t="str">
         <x:v>Record adopt, pilot, conditional use, restrict, defer, redesign, reject, or retire, together with conditions and review date.</x:v>
       </x:c>
-      <x:c r="C17" s="17" t="str"/>
+      <x:c r="C17" s="17"/>
+      <x:c r="D17"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:F1"/>
+    <x:mergeCell ref="A1:D1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R46a175a0141a4f6e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9b1e0eb7a7f54d56"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1596,23 +2190,29 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="29" t="str">
+      <x:c r="A1" s="78" t="str">
         <x:v>AIHE-B05 — Model Selection, Uncertainty, and Reproducibility</x:v>
       </x:c>
-      <x:c r="B1" s="29"/>
-      <x:c r="C1" s="29"/>
-      <x:c r="D1" s="29"/>
+      <x:c r="B1" s="78"/>
+      <x:c r="C1" s="78"/>
+      <x:c r="D1" s="78"/>
       <x:c r="E1" s="29"/>
       <x:c r="F1" s="29"/>
     </x:row>
+    <x:row r="2">
+      <x:c r="A2"/>
+      <x:c r="B2"/>
+      <x:c r="C2"/>
+      <x:c r="D2"/>
+    </x:row>
     <x:row r="3">
-      <x:c r="A3" s="33" t="str">
+      <x:c r="A3" s="80" t="str">
         <x:v>Primary chapter</x:v>
       </x:c>
       <x:c r="B3" s="17" t="str">
         <x:v>8 — Decision Modelling and Simulation Under Uncertainty</x:v>
       </x:c>
-      <x:c r="C3" s="33" t="str">
+      <x:c r="C3" s="80" t="str">
         <x:v>Release</x:v>
       </x:c>
       <x:c r="D3" s="17" t="str">
@@ -1620,13 +2220,13 @@
       </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="33" t="str">
+      <x:c r="A4" s="80" t="str">
         <x:v>Purpose</x:v>
       </x:c>
       <x:c r="B4" s="17" t="str">
         <x:v>Select a decision model from the problem structure and document evidence, verification, uncertainty, and reproducibility.</x:v>
       </x:c>
-      <x:c r="C4" s="33" t="str">
+      <x:c r="C4" s="80" t="str">
         <x:v>Reader level</x:v>
       </x:c>
       <x:c r="D4" s="17" t="str">
@@ -1634,13 +2234,13 @@
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="33" t="str">
+      <x:c r="A5" s="80" t="str">
         <x:v>Required inputs</x:v>
       </x:c>
       <x:c r="B5" s="17" t="str">
         <x:v>Defined decision problem, realistic comparator, local evidence, named owners, and applicable institutional requirements</x:v>
       </x:c>
-      <x:c r="C5" s="33" t="str">
+      <x:c r="C5" s="80" t="str">
         <x:v>Expected output</x:v>
       </x:c>
       <x:c r="D5" s="17" t="str">
@@ -1661,6 +2261,12 @@
         <x:v>60–180 minutes</x:v>
       </x:c>
     </x:row>
+    <x:row r="7">
+      <x:c r="A7"/>
+      <x:c r="B7"/>
+      <x:c r="C7"/>
+      <x:c r="D7"/>
+    </x:row>
     <x:row r="8">
       <x:c r="A8" s="23" t="str">
         <x:v>Decision structure</x:v>
@@ -1739,7 +2345,7 @@
         <x:v>Agent-based, system-dynamics, or hybrid model</x:v>
       </x:c>
       <x:c r="C13" s="17" t="str">
-        <x:v>Behavior rules, networks, stocks, flows, delays, and feedback</x:v>
+        <x:v>Behaviour rules, networks, stocks, flows, delays, and feedback</x:v>
       </x:c>
       <x:c r="D13" s="17" t="str">
         <x:v>Pattern validation, sensitivity to rules, alternative structures</x:v>
@@ -1762,10 +2368,11 @@
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:F1"/>
+    <x:mergeCell ref="A1:D1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7cc98bf56f02498b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8e4ef25ec73f4ca1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1783,56 +2390,70 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="29" t="str">
+      <x:c r="A1" s="78" t="str">
         <x:v>AIHE-D01 — Vendor Evidence and Contract Requirements</x:v>
       </x:c>
-      <x:c r="B1" s="29"/>
-      <x:c r="C1" s="29"/>
-      <x:c r="D1" s="29"/>
-      <x:c r="E1" s="29"/>
-      <x:c r="F1" s="29"/>
+      <x:c r="B1" s="78"/>
+      <x:c r="C1" s="78"/>
+      <x:c r="D1" s="78"/>
+      <x:c r="E1" s="78"/>
+      <x:c r="F1" s="78"/>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2"/>
+      <x:c r="B2"/>
+      <x:c r="C2"/>
+      <x:c r="D2"/>
+      <x:c r="E2"/>
+      <x:c r="F2"/>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="33" t="str">
+      <x:c r="A3" s="80" t="str">
         <x:v>Primary chapter</x:v>
       </x:c>
       <x:c r="B3" s="17" t="str">
         <x:v>9 — Problem-First Procurement and Vendor Governance</x:v>
       </x:c>
-      <x:c r="C3" s="33" t="str">
+      <x:c r="C3" s="80" t="str">
         <x:v>Release</x:v>
       </x:c>
       <x:c r="D3" s="17" t="str">
         <x:v>V1.0</x:v>
       </x:c>
+      <x:c r="E3"/>
+      <x:c r="F3"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="33" t="str">
+      <x:c r="A4" s="80" t="str">
         <x:v>Purpose</x:v>
       </x:c>
       <x:c r="B4" s="17" t="str">
         <x:v>Translate evidence, interoperability, data, security, monitoring, update, service, remedy, portability, and exit requirements into contract terms.</x:v>
       </x:c>
-      <x:c r="C4" s="33" t="str">
+      <x:c r="C4" s="80" t="str">
         <x:v>Reader level</x:v>
       </x:c>
       <x:c r="D4" s="17" t="str">
         <x:v>Applied</x:v>
       </x:c>
+      <x:c r="E4"/>
+      <x:c r="F4"/>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="33" t="str">
+      <x:c r="A5" s="80" t="str">
         <x:v>Required inputs</x:v>
       </x:c>
       <x:c r="B5" s="17" t="str">
         <x:v>Defined decision problem, realistic comparator, local evidence, named owners, and applicable institutional requirements</x:v>
       </x:c>
-      <x:c r="C5" s="33" t="str">
+      <x:c r="C5" s="80" t="str">
         <x:v>Expected output</x:v>
       </x:c>
       <x:c r="D5" s="17" t="str">
         <x:v>Versioned institutional decision record with conditions, monitoring, review date, and exit route</x:v>
       </x:c>
+      <x:c r="E5"/>
+      <x:c r="F5"/>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="33" t="str">
@@ -1847,6 +2468,16 @@
       <x:c r="D6" s="17" t="str">
         <x:v>60–180 minutes</x:v>
       </x:c>
+      <x:c r="E6"/>
+      <x:c r="F6"/>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7"/>
+      <x:c r="B7"/>
+      <x:c r="C7"/>
+      <x:c r="D7"/>
+      <x:c r="E7"/>
+      <x:c r="F7"/>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="23" t="str">
@@ -1872,91 +2503,91 @@
       <x:c r="A9" s="17" t="str">
         <x:v>Intended use, excluded use, population, and version</x:v>
       </x:c>
-      <x:c r="B9" s="17" t="str"/>
-      <x:c r="C9" s="17" t="str"/>
-      <x:c r="D9" s="17" t="str"/>
-      <x:c r="E9" s="17" t="str"/>
-      <x:c r="F9" s="17" t="str"/>
+      <x:c r="B9" s="17"/>
+      <x:c r="C9" s="17"/>
+      <x:c r="D9" s="17"/>
+      <x:c r="E9" s="17"/>
+      <x:c r="F9" s="17"/>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="17" t="str">
         <x:v>Clinical, technical, human-factors, and economic evidence</x:v>
       </x:c>
-      <x:c r="B10" s="17" t="str"/>
-      <x:c r="C10" s="17" t="str"/>
-      <x:c r="D10" s="17" t="str"/>
-      <x:c r="E10" s="17" t="str"/>
-      <x:c r="F10" s="17" t="str"/>
+      <x:c r="B10" s="17"/>
+      <x:c r="C10" s="17"/>
+      <x:c r="D10" s="17"/>
+      <x:c r="E10" s="17"/>
+      <x:c r="F10" s="17"/>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="17" t="str">
         <x:v>Interoperability, data quality, provenance, and portability</x:v>
       </x:c>
-      <x:c r="B11" s="17" t="str"/>
-      <x:c r="C11" s="17" t="str"/>
-      <x:c r="D11" s="17" t="str"/>
-      <x:c r="E11" s="17" t="str"/>
-      <x:c r="F11" s="17" t="str"/>
+      <x:c r="B11" s="17"/>
+      <x:c r="C11" s="17"/>
+      <x:c r="D11" s="17"/>
+      <x:c r="E11" s="17"/>
+      <x:c r="F11" s="17"/>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="17" t="str">
         <x:v>Privacy, cybersecurity, resilience, subprocessors, and incidents</x:v>
       </x:c>
-      <x:c r="B12" s="17" t="str"/>
-      <x:c r="C12" s="17" t="str"/>
-      <x:c r="D12" s="17" t="str"/>
-      <x:c r="E12" s="17" t="str"/>
-      <x:c r="F12" s="17" t="str"/>
+      <x:c r="B12" s="17"/>
+      <x:c r="C12" s="17"/>
+      <x:c r="D12" s="17"/>
+      <x:c r="E12" s="17"/>
+      <x:c r="F12" s="17"/>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="17" t="str">
         <x:v>Pricing units, volume exposure, integration, support, and escalation</x:v>
       </x:c>
-      <x:c r="B13" s="17" t="str"/>
-      <x:c r="C13" s="17" t="str"/>
-      <x:c r="D13" s="17" t="str"/>
-      <x:c r="E13" s="17" t="str"/>
-      <x:c r="F13" s="17" t="str"/>
+      <x:c r="B13" s="17"/>
+      <x:c r="C13" s="17"/>
+      <x:c r="D13" s="17"/>
+      <x:c r="E13" s="17"/>
+      <x:c r="F13" s="17"/>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="17" t="str">
         <x:v>Updates, material change, validation, approval, rollback, and notice</x:v>
       </x:c>
-      <x:c r="B14" s="17" t="str"/>
-      <x:c r="C14" s="17" t="str"/>
-      <x:c r="D14" s="17" t="str"/>
-      <x:c r="E14" s="17" t="str"/>
-      <x:c r="F14" s="17" t="str"/>
+      <x:c r="B14" s="17"/>
+      <x:c r="C14" s="17"/>
+      <x:c r="D14" s="17"/>
+      <x:c r="E14" s="17"/>
+      <x:c r="F14" s="17"/>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="17" t="str">
         <x:v>Monitoring data, audit rights, logs, model card, and assurance cooperation</x:v>
       </x:c>
-      <x:c r="B15" s="17" t="str"/>
-      <x:c r="C15" s="17" t="str"/>
-      <x:c r="D15" s="17" t="str"/>
-      <x:c r="E15" s="17" t="str"/>
-      <x:c r="F15" s="17" t="str"/>
+      <x:c r="B15" s="17"/>
+      <x:c r="C15" s="17"/>
+      <x:c r="D15" s="17"/>
+      <x:c r="E15" s="17"/>
+      <x:c r="F15" s="17"/>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="17" t="str">
         <x:v>Service levels, downtime, fallback, continuity, and support</x:v>
       </x:c>
-      <x:c r="B16" s="17" t="str"/>
-      <x:c r="C16" s="17" t="str"/>
-      <x:c r="D16" s="17" t="str"/>
-      <x:c r="E16" s="17" t="str"/>
-      <x:c r="F16" s="17" t="str"/>
+      <x:c r="B16" s="17"/>
+      <x:c r="C16" s="17"/>
+      <x:c r="D16" s="17"/>
+      <x:c r="E16" s="17"/>
+      <x:c r="F16" s="17"/>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="17" t="str">
         <x:v>Termination, transition, deletion, archive, take-back, and decommissioning</x:v>
       </x:c>
-      <x:c r="B17" s="17" t="str"/>
-      <x:c r="C17" s="17" t="str"/>
-      <x:c r="D17" s="17" t="str"/>
-      <x:c r="E17" s="17" t="str"/>
-      <x:c r="F17" s="17" t="str"/>
+      <x:c r="B17" s="17"/>
+      <x:c r="C17" s="17"/>
+      <x:c r="D17" s="17"/>
+      <x:c r="E17" s="17"/>
+      <x:c r="F17" s="17"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -1964,7 +2595,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R14411776542849e3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4acc2c0514504df3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1980,23 +2611,29 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="29" t="str">
+      <x:c r="A1" s="78" t="str">
         <x:v>AIHE-C03 — Integrated Institutional-Risk Review</x:v>
       </x:c>
-      <x:c r="B1" s="29"/>
-      <x:c r="C1" s="29"/>
-      <x:c r="D1" s="29"/>
+      <x:c r="B1" s="78"/>
+      <x:c r="C1" s="78"/>
+      <x:c r="D1" s="78"/>
       <x:c r="E1" s="29"/>
       <x:c r="F1" s="29"/>
     </x:row>
+    <x:row r="2">
+      <x:c r="A2"/>
+      <x:c r="B2"/>
+      <x:c r="C2"/>
+      <x:c r="D2"/>
+    </x:row>
     <x:row r="3">
-      <x:c r="A3" s="33" t="str">
+      <x:c r="A3" s="80" t="str">
         <x:v>Primary chapter</x:v>
       </x:c>
       <x:c r="B3" s="17" t="str">
         <x:v>10 — Governance, Accountability, and Institutional Risk</x:v>
       </x:c>
-      <x:c r="C3" s="33" t="str">
+      <x:c r="C3" s="80" t="str">
         <x:v>Release</x:v>
       </x:c>
       <x:c r="D3" s="17" t="str">
@@ -2004,13 +2641,13 @@
       </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="33" t="str">
+      <x:c r="A4" s="80" t="str">
         <x:v>Purpose</x:v>
       </x:c>
       <x:c r="B4" s="17" t="str">
         <x:v>Review ethics, equity, privacy, cybersecurity, safety, continuity, trust, legal, and economic risks as one institutional system.</x:v>
       </x:c>
-      <x:c r="C4" s="33" t="str">
+      <x:c r="C4" s="80" t="str">
         <x:v>Reader level</x:v>
       </x:c>
       <x:c r="D4" s="17" t="str">
@@ -2018,13 +2655,13 @@
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="33" t="str">
+      <x:c r="A5" s="80" t="str">
         <x:v>Required inputs</x:v>
       </x:c>
       <x:c r="B5" s="17" t="str">
         <x:v>Defined decision problem, realistic comparator, local evidence, named owners, and applicable institutional requirements</x:v>
       </x:c>
-      <x:c r="C5" s="33" t="str">
+      <x:c r="C5" s="80" t="str">
         <x:v>Expected output</x:v>
       </x:c>
       <x:c r="D5" s="17" t="str">
@@ -2045,6 +2682,12 @@
         <x:v>60–180 minutes</x:v>
       </x:c>
     </x:row>
+    <x:row r="7">
+      <x:c r="A7"/>
+      <x:c r="B7"/>
+      <x:c r="C7"/>
+      <x:c r="D7"/>
+    </x:row>
     <x:row r="8">
       <x:c r="A8" s="23" t="str">
         <x:v>Domain</x:v>
@@ -2066,8 +2709,8 @@
       <x:c r="B9" s="17" t="str">
         <x:v>Are people informed appropriately, able to question consequential use, and offered a human route where required?</x:v>
       </x:c>
-      <x:c r="C9" s="17" t="str"/>
-      <x:c r="D9" s="17" t="str"/>
+      <x:c r="C9" s="17"/>
+      <x:c r="D9" s="17"/>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="17" t="str">
@@ -2076,8 +2719,8 @@
       <x:c r="B10" s="17" t="str">
         <x:v>Are intended use, limitations, local performance, workflow controls, and fallback acceptable?</x:v>
       </x:c>
-      <x:c r="C10" s="17" t="str"/>
-      <x:c r="D10" s="17" t="str"/>
+      <x:c r="C10" s="17"/>
+      <x:c r="D10" s="17"/>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="17" t="str">
@@ -2086,8 +2729,8 @@
       <x:c r="B11" s="17" t="str">
         <x:v>Are data, performance, access, outcomes, and burdens assessed across relevant groups?</x:v>
       </x:c>
-      <x:c r="C11" s="17" t="str"/>
-      <x:c r="D11" s="17" t="str"/>
+      <x:c r="C11" s="17"/>
+      <x:c r="D11" s="17"/>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="17" t="str">
@@ -2096,8 +2739,8 @@
       <x:c r="B12" s="17" t="str">
         <x:v>Are purpose, necessity, minimization, authority, retention, access, and secondary use governed?</x:v>
       </x:c>
-      <x:c r="C12" s="17" t="str"/>
-      <x:c r="D12" s="17" t="str"/>
+      <x:c r="C12" s="17"/>
+      <x:c r="D12" s="17"/>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="17" t="str">
@@ -2106,8 +2749,8 @@
       <x:c r="B13" s="17" t="str">
         <x:v>Are threat, supplier, integration, logging, incident, downtime, recovery, and continuity controls adequate?</x:v>
       </x:c>
-      <x:c r="C13" s="17" t="str"/>
-      <x:c r="D13" s="17" t="str"/>
+      <x:c r="C13" s="17"/>
+      <x:c r="D13" s="17"/>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="17" t="str">
@@ -2116,8 +2759,8 @@
       <x:c r="B14" s="17" t="str">
         <x:v>Are evidence, uncertainty, limitations, responsibilities, incidents, and communication credible and accessible?</x:v>
       </x:c>
-      <x:c r="C14" s="17" t="str"/>
-      <x:c r="D14" s="17" t="str"/>
+      <x:c r="C14" s="17"/>
+      <x:c r="D14" s="17"/>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="17" t="str">
@@ -2126,16 +2769,17 @@
       <x:c r="B15" s="17" t="str">
         <x:v>Are decision rights, review workload, escalation, pause, update, restart, renewal, and retirement authority explicit?</x:v>
       </x:c>
-      <x:c r="C15" s="17" t="str"/>
-      <x:c r="D15" s="17" t="str"/>
+      <x:c r="C15" s="17"/>
+      <x:c r="D15" s="17"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:F1"/>
+    <x:mergeCell ref="A1:D1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9bfdf983a461411b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0e5cf44c9d884a71"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2149,23 +2793,29 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="29" t="str">
+      <x:c r="A1" s="78" t="str">
         <x:v>AIHE-C05 — Public Transparency and Communication Record</x:v>
       </x:c>
-      <x:c r="B1" s="29"/>
-      <x:c r="C1" s="29"/>
-      <x:c r="D1" s="29"/>
+      <x:c r="B1" s="78"/>
+      <x:c r="C1" s="78"/>
+      <x:c r="D1" s="78"/>
       <x:c r="E1" s="29"/>
       <x:c r="F1" s="29"/>
     </x:row>
+    <x:row r="2">
+      <x:c r="A2"/>
+      <x:c r="B2"/>
+      <x:c r="C2"/>
+      <x:c r="D2"/>
+    </x:row>
     <x:row r="3">
-      <x:c r="A3" s="33" t="str">
+      <x:c r="A3" s="80" t="str">
         <x:v>Primary chapter</x:v>
       </x:c>
       <x:c r="B3" s="17" t="str">
         <x:v>10 — Governance, Accountability, and Institutional Risk</x:v>
       </x:c>
-      <x:c r="C3" s="33" t="str">
+      <x:c r="C3" s="80" t="str">
         <x:v>Release</x:v>
       </x:c>
       <x:c r="D3" s="17" t="str">
@@ -2173,13 +2823,13 @@
       </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="33" t="str">
+      <x:c r="A4" s="80" t="str">
         <x:v>Purpose</x:v>
       </x:c>
       <x:c r="B4" s="17" t="str">
         <x:v>Define accurate, accessible communication about intended use, limitations, oversight, data, complaints, incidents, and alternatives.</x:v>
       </x:c>
-      <x:c r="C4" s="33" t="str">
+      <x:c r="C4" s="80" t="str">
         <x:v>Reader level</x:v>
       </x:c>
       <x:c r="D4" s="17" t="str">
@@ -2187,13 +2837,13 @@
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="33" t="str">
+      <x:c r="A5" s="80" t="str">
         <x:v>Required inputs</x:v>
       </x:c>
       <x:c r="B5" s="17" t="str">
         <x:v>Defined decision problem, realistic comparator, local evidence, named owners, and applicable institutional requirements</x:v>
       </x:c>
-      <x:c r="C5" s="33" t="str">
+      <x:c r="C5" s="80" t="str">
         <x:v>Expected output</x:v>
       </x:c>
       <x:c r="D5" s="17" t="str">
@@ -2214,6 +2864,12 @@
         <x:v>60–180 minutes</x:v>
       </x:c>
     </x:row>
+    <x:row r="7">
+      <x:c r="A7"/>
+      <x:c r="B7"/>
+      <x:c r="C7"/>
+      <x:c r="D7"/>
+    </x:row>
     <x:row r="8">
       <x:c r="A8" s="23" t="str">
         <x:v>Communication element</x:v>
@@ -2221,62 +2877,81 @@
       <x:c r="B8" s="23" t="str">
         <x:v>Approved content, channel, owner, and review</x:v>
       </x:c>
+      <x:c r="C8"/>
+      <x:c r="D8"/>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="17" t="str">
         <x:v>Purpose and intended use</x:v>
       </x:c>
-      <x:c r="B9" s="17" t="str"/>
+      <x:c r="B9" s="17"/>
+      <x:c r="C9"/>
+      <x:c r="D9"/>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="17" t="str">
         <x:v>What the system does and does not do</x:v>
       </x:c>
-      <x:c r="B10" s="17" t="str"/>
+      <x:c r="B10" s="17"/>
+      <x:c r="C10"/>
+      <x:c r="D10"/>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="17" t="str">
         <x:v>Role of human review and accountability</x:v>
       </x:c>
-      <x:c r="B11" s="17" t="str"/>
+      <x:c r="B11" s="17"/>
+      <x:c r="C11"/>
+      <x:c r="D11"/>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="17" t="str">
         <x:v>Data use, privacy, retention, and external providers</x:v>
       </x:c>
-      <x:c r="B12" s="17" t="str"/>
+      <x:c r="B12" s="17"/>
+      <x:c r="C12"/>
+      <x:c r="D12"/>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="17" t="str">
         <x:v>Known limitations, uncertainty, and subgroup concerns</x:v>
       </x:c>
-      <x:c r="B13" s="17" t="str"/>
+      <x:c r="B13" s="17"/>
+      <x:c r="C13"/>
+      <x:c r="D13"/>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="17" t="str">
         <x:v>Accessibility, language, disability, and non-digital alternatives</x:v>
       </x:c>
-      <x:c r="B14" s="17" t="str"/>
+      <x:c r="B14" s="17"/>
+      <x:c r="C14"/>
+      <x:c r="D14"/>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="17" t="str">
         <x:v>Questions, complaints, contestability, and incident communication</x:v>
       </x:c>
-      <x:c r="B15" s="17" t="str"/>
+      <x:c r="B15" s="17"/>
+      <x:c r="C15"/>
+      <x:c r="D15"/>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="17" t="str">
         <x:v>Material changes, suspension, and retirement</x:v>
       </x:c>
-      <x:c r="B16" s="17" t="str"/>
+      <x:c r="B16" s="17"/>
+      <x:c r="C16"/>
+      <x:c r="D16"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:F1"/>
+    <x:mergeCell ref="A1:D1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re009867a1f0b4f73"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1af3e89abe6a4a6f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2293,56 +2968,66 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="29" t="str">
+      <x:c r="A1" s="78" t="str">
         <x:v>AIHE-D02 — Lifecycle Gates, Staged Implementation, and Dossier Status</x:v>
       </x:c>
-      <x:c r="B1" s="29"/>
-      <x:c r="C1" s="29"/>
-      <x:c r="D1" s="29"/>
-      <x:c r="E1" s="29"/>
+      <x:c r="B1" s="78"/>
+      <x:c r="C1" s="78"/>
+      <x:c r="D1" s="78"/>
+      <x:c r="E1" s="78"/>
       <x:c r="F1" s="29"/>
     </x:row>
+    <x:row r="2">
+      <x:c r="A2"/>
+      <x:c r="B2"/>
+      <x:c r="C2"/>
+      <x:c r="D2"/>
+      <x:c r="E2"/>
+    </x:row>
     <x:row r="3">
-      <x:c r="A3" s="33" t="str">
+      <x:c r="A3" s="80" t="str">
         <x:v>Primary chapter</x:v>
       </x:c>
       <x:c r="B3" s="17" t="str">
         <x:v>12 — Decision Architecture and Lifecycle Governance</x:v>
       </x:c>
-      <x:c r="C3" s="33" t="str">
+      <x:c r="C3" s="80" t="str">
         <x:v>Release</x:v>
       </x:c>
       <x:c r="D3" s="17" t="str">
         <x:v>V1.0</x:v>
       </x:c>
+      <x:c r="E3"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="33" t="str">
+      <x:c r="A4" s="80" t="str">
         <x:v>Purpose</x:v>
       </x:c>
       <x:c r="B4" s="17" t="str">
         <x:v>Control increasing commitment through problem, readiness, evidence, local validation, economics, pilot, scale, renewal, and retirement gates.</x:v>
       </x:c>
-      <x:c r="C4" s="33" t="str">
+      <x:c r="C4" s="80" t="str">
         <x:v>Reader level</x:v>
       </x:c>
       <x:c r="D4" s="17" t="str">
         <x:v>Applied</x:v>
       </x:c>
+      <x:c r="E4"/>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="33" t="str">
+      <x:c r="A5" s="80" t="str">
         <x:v>Required inputs</x:v>
       </x:c>
       <x:c r="B5" s="17" t="str">
         <x:v>Defined decision problem, realistic comparator, local evidence, named owners, and applicable institutional requirements</x:v>
       </x:c>
-      <x:c r="C5" s="33" t="str">
+      <x:c r="C5" s="80" t="str">
         <x:v>Expected output</x:v>
       </x:c>
       <x:c r="D5" s="17" t="str">
         <x:v>Versioned institutional decision record with conditions, monitoring, review date, and exit route</x:v>
       </x:c>
+      <x:c r="E5"/>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="33" t="str">
@@ -2357,6 +3042,14 @@
       <x:c r="D6" s="17" t="str">
         <x:v>60–180 minutes</x:v>
       </x:c>
+      <x:c r="E6"/>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7"/>
+      <x:c r="B7"/>
+      <x:c r="C7"/>
+      <x:c r="D7"/>
+      <x:c r="E7"/>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="23" t="str">
@@ -2382,9 +3075,9 @@
       <x:c r="B9" s="17" t="str">
         <x:v>Baseline burden, alternatives, intended action, outcomes, and opportunity cost</x:v>
       </x:c>
-      <x:c r="C9" s="17" t="str"/>
-      <x:c r="D9" s="17" t="str"/>
-      <x:c r="E9" s="17" t="str"/>
+      <x:c r="C9" s="17"/>
+      <x:c r="D9" s="17"/>
+      <x:c r="E9" s="17"/>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="17" t="str">
@@ -2393,9 +3086,9 @@
       <x:c r="B10" s="17" t="str">
         <x:v>Infrastructure, data fitness, workflow, workforce, quality, governance, and capacity</x:v>
       </x:c>
-      <x:c r="C10" s="17" t="str"/>
-      <x:c r="D10" s="17" t="str"/>
-      <x:c r="E10" s="17" t="str"/>
+      <x:c r="C10" s="17"/>
+      <x:c r="D10" s="17"/>
+      <x:c r="E10" s="17"/>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="17" t="str">
@@ -2404,9 +3097,9 @@
       <x:c r="B11" s="17" t="str">
         <x:v>Exact version, applicability, independent appraisal, limitations, and claim challenge</x:v>
       </x:c>
-      <x:c r="C11" s="17" t="str"/>
-      <x:c r="D11" s="17" t="str"/>
-      <x:c r="E11" s="17" t="str"/>
+      <x:c r="C11" s="17"/>
+      <x:c r="D11" s="17"/>
+      <x:c r="E11" s="17"/>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="17" t="str">
@@ -2415,9 +3108,9 @@
       <x:c r="B12" s="17" t="str">
         <x:v>Technical and human–AI performance, subgroups, workflow, safety, and monitoring feasibility</x:v>
       </x:c>
-      <x:c r="C12" s="17" t="str"/>
-      <x:c r="D12" s="17" t="str"/>
-      <x:c r="E12" s="17" t="str"/>
+      <x:c r="C12" s="17"/>
+      <x:c r="D12" s="17"/>
+      <x:c r="E12" s="17"/>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="17" t="str">
@@ -2426,9 +3119,9 @@
       <x:c r="B13" s="17" t="str">
         <x:v>Lifecycle cost, pricing, outcomes, budget impact, uncertainty, and benefit realization</x:v>
       </x:c>
-      <x:c r="C13" s="17" t="str"/>
-      <x:c r="D13" s="17" t="str"/>
-      <x:c r="E13" s="17" t="str"/>
+      <x:c r="C13" s="17"/>
+      <x:c r="D13" s="17"/>
+      <x:c r="E13" s="17"/>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="17" t="str">
@@ -2437,9 +3130,9 @@
       <x:c r="B14" s="17" t="str">
         <x:v>Training, fallback, incident process, measures, thresholds, duration, and decision criteria</x:v>
       </x:c>
-      <x:c r="C14" s="17" t="str"/>
-      <x:c r="D14" s="17" t="str"/>
-      <x:c r="E14" s="17" t="str"/>
+      <x:c r="C14" s="17"/>
+      <x:c r="D14" s="17"/>
+      <x:c r="E14" s="17"/>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="17" t="str">
@@ -2448,9 +3141,9 @@
       <x:c r="B15" s="17" t="str">
         <x:v>Transfer conditions, implementation strategies, governance capacity, contract, and portfolio effects</x:v>
       </x:c>
-      <x:c r="C15" s="17" t="str"/>
-      <x:c r="D15" s="17" t="str"/>
-      <x:c r="E15" s="17" t="str"/>
+      <x:c r="C15" s="17"/>
+      <x:c r="D15" s="17"/>
+      <x:c r="E15" s="17"/>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="17" t="str">
@@ -2459,17 +3152,18 @@
       <x:c r="B16" s="17" t="str">
         <x:v>Current comparator, evidence, value, safeguards, material changes, alternatives, and exit</x:v>
       </x:c>
-      <x:c r="C16" s="17" t="str"/>
-      <x:c r="D16" s="17" t="str"/>
-      <x:c r="E16" s="17" t="str"/>
+      <x:c r="C16" s="17"/>
+      <x:c r="D16" s="17"/>
+      <x:c r="E16" s="17"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:F1"/>
+    <x:mergeCell ref="A1:E1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbecf12bdff56469c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2b07b81a04414e11"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2485,23 +3179,29 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="29" t="str">
+      <x:c r="A1" s="78" t="str">
         <x:v>AIHE-D03 — Post-Deployment Monitoring and Algorithmovigilance Cadence</x:v>
       </x:c>
-      <x:c r="B1" s="29"/>
-      <x:c r="C1" s="29"/>
-      <x:c r="D1" s="29"/>
+      <x:c r="B1" s="78"/>
+      <x:c r="C1" s="78"/>
+      <x:c r="D1" s="78"/>
       <x:c r="E1" s="29"/>
       <x:c r="F1" s="29"/>
     </x:row>
+    <x:row r="2">
+      <x:c r="A2"/>
+      <x:c r="B2"/>
+      <x:c r="C2"/>
+      <x:c r="D2"/>
+    </x:row>
     <x:row r="3">
-      <x:c r="A3" s="33" t="str">
+      <x:c r="A3" s="80" t="str">
         <x:v>Primary chapter</x:v>
       </x:c>
       <x:c r="B3" s="17" t="str">
         <x:v>12 — Decision Architecture and Lifecycle Governance</x:v>
       </x:c>
-      <x:c r="C3" s="33" t="str">
+      <x:c r="C3" s="80" t="str">
         <x:v>Release</x:v>
       </x:c>
       <x:c r="D3" s="17" t="str">
@@ -2509,13 +3209,13 @@
       </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="33" t="str">
+      <x:c r="A4" s="80" t="str">
         <x:v>Purpose</x:v>
       </x:c>
       <x:c r="B4" s="17" t="str">
         <x:v>Define recurring and event-triggered surveillance across technical, workflow, safety, equity, economic, and contractual domains.</x:v>
       </x:c>
-      <x:c r="C4" s="33" t="str">
+      <x:c r="C4" s="80" t="str">
         <x:v>Reader level</x:v>
       </x:c>
       <x:c r="D4" s="17" t="str">
@@ -2523,13 +3223,13 @@
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="33" t="str">
+      <x:c r="A5" s="80" t="str">
         <x:v>Required inputs</x:v>
       </x:c>
       <x:c r="B5" s="17" t="str">
         <x:v>Defined decision problem, realistic comparator, local evidence, named owners, and applicable institutional requirements</x:v>
       </x:c>
-      <x:c r="C5" s="33" t="str">
+      <x:c r="C5" s="80" t="str">
         <x:v>Expected output</x:v>
       </x:c>
       <x:c r="D5" s="17" t="str">
@@ -2550,6 +3250,12 @@
         <x:v>60–180 minutes</x:v>
       </x:c>
     </x:row>
+    <x:row r="7">
+      <x:c r="A7"/>
+      <x:c r="B7"/>
+      <x:c r="C7"/>
+      <x:c r="D7"/>
+    </x:row>
     <x:row r="8">
       <x:c r="A8" s="23" t="str">
         <x:v>Frequency</x:v>
@@ -2651,10 +3357,11 @@
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:F1"/>
+    <x:mergeCell ref="A1:D1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3ea24c3e56b2469b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6fe5f23e19dc49d4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2675,31 +3382,31 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="23" t="str">
+      <x:c r="A1" s="74" t="str">
         <x:v>Part</x:v>
       </x:c>
-      <x:c r="B1" s="23" t="str">
+      <x:c r="B1" s="74" t="str">
         <x:v>Part title</x:v>
       </x:c>
-      <x:c r="C1" s="23" t="str">
+      <x:c r="C1" s="74" t="str">
         <x:v>Chapter</x:v>
       </x:c>
-      <x:c r="D1" s="23" t="str">
+      <x:c r="D1" s="74" t="str">
         <x:v>Chapter title</x:v>
       </x:c>
-      <x:c r="E1" s="23" t="str">
+      <x:c r="E1" s="74" t="str">
         <x:v>Resource ID</x:v>
       </x:c>
-      <x:c r="F1" s="23" t="str">
+      <x:c r="F1" s="74" t="str">
         <x:v>Resource title</x:v>
       </x:c>
-      <x:c r="G1" s="23" t="str">
+      <x:c r="G1" s="74" t="str">
         <x:v>Reader level</x:v>
       </x:c>
-      <x:c r="H1" s="23" t="str">
+      <x:c r="H1" s="74" t="str">
         <x:v>Estimated time</x:v>
       </x:c>
-      <x:c r="I1" s="23" t="str">
+      <x:c r="I1" s="74" t="str">
         <x:v>Worksheet</x:v>
       </x:c>
     </x:row>
@@ -3402,7 +4109,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc1578983805a4ebc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1acdc6d0726446bd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3417,23 +4124,29 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="29" t="str">
+      <x:c r="A1" s="78" t="str">
         <x:v>AIHE-D04 — Incident Classification and Reconstruction</x:v>
       </x:c>
-      <x:c r="B1" s="29"/>
-      <x:c r="C1" s="29"/>
-      <x:c r="D1" s="29"/>
+      <x:c r="B1" s="78"/>
+      <x:c r="C1" s="78"/>
+      <x:c r="D1" s="78"/>
       <x:c r="E1" s="29"/>
       <x:c r="F1" s="29"/>
     </x:row>
+    <x:row r="2">
+      <x:c r="A2"/>
+      <x:c r="B2"/>
+      <x:c r="C2"/>
+      <x:c r="D2"/>
+    </x:row>
     <x:row r="3">
-      <x:c r="A3" s="33" t="str">
+      <x:c r="A3" s="80" t="str">
         <x:v>Primary chapter</x:v>
       </x:c>
       <x:c r="B3" s="17" t="str">
         <x:v>12 — Decision Architecture and Lifecycle Governance</x:v>
       </x:c>
-      <x:c r="C3" s="33" t="str">
+      <x:c r="C3" s="80" t="str">
         <x:v>Release</x:v>
       </x:c>
       <x:c r="D3" s="17" t="str">
@@ -3441,13 +4154,13 @@
       </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="33" t="str">
+      <x:c r="A4" s="80" t="str">
         <x:v>Purpose</x:v>
       </x:c>
       <x:c r="B4" s="17" t="str">
         <x:v>Reconstruct technical, clinical, workflow, privacy, cybersecurity, equity, communication, and economic incidents consistently.</x:v>
       </x:c>
-      <x:c r="C4" s="33" t="str">
+      <x:c r="C4" s="80" t="str">
         <x:v>Reader level</x:v>
       </x:c>
       <x:c r="D4" s="17" t="str">
@@ -3455,13 +4168,13 @@
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="33" t="str">
+      <x:c r="A5" s="80" t="str">
         <x:v>Required inputs</x:v>
       </x:c>
       <x:c r="B5" s="17" t="str">
         <x:v>Defined decision problem, realistic comparator, local evidence, named owners, and applicable institutional requirements</x:v>
       </x:c>
-      <x:c r="C5" s="33" t="str">
+      <x:c r="C5" s="80" t="str">
         <x:v>Expected output</x:v>
       </x:c>
       <x:c r="D5" s="17" t="str">
@@ -3482,6 +4195,12 @@
         <x:v>60–180 minutes</x:v>
       </x:c>
     </x:row>
+    <x:row r="7">
+      <x:c r="A7"/>
+      <x:c r="B7"/>
+      <x:c r="C7"/>
+      <x:c r="D7"/>
+    </x:row>
     <x:row r="8">
       <x:c r="A8" s="23" t="str">
         <x:v>Field</x:v>
@@ -3492,6 +4211,7 @@
       <x:c r="C8" s="23" t="str">
         <x:v>Institutional response</x:v>
       </x:c>
+      <x:c r="D8"/>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="17" t="str">
@@ -3500,7 +4220,8 @@
       <x:c r="B9" s="17" t="str">
         <x:v>Describe the event or pattern, who detected it, and how it was classified.</x:v>
       </x:c>
-      <x:c r="C9" s="17" t="str"/>
+      <x:c r="C9" s="17"/>
+      <x:c r="D9"/>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="17" t="str">
@@ -3509,7 +4230,8 @@
       <x:c r="B10" s="17" t="str">
         <x:v>Preserve available data, source, timestamp, transformation, missingness, quality state, and recent source changes.</x:v>
       </x:c>
-      <x:c r="C10" s="17" t="str"/>
+      <x:c r="C10" s="17"/>
+      <x:c r="D10"/>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="17" t="str">
@@ -3518,7 +4240,8 @@
       <x:c r="B11" s="17" t="str">
         <x:v>Record model, software, threshold, interface, prompt, template, retrieval, knowledge source, and hosting versions.</x:v>
       </x:c>
-      <x:c r="C11" s="17" t="str"/>
+      <x:c r="C11" s="17"/>
+      <x:c r="D11"/>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="17" t="str">
@@ -3527,7 +4250,8 @@
       <x:c r="B12" s="17" t="str">
         <x:v>Preserve score, classification, recommendation, generated content, alert, action, explanation, and uncertainty.</x:v>
       </x:c>
-      <x:c r="C12" s="17" t="str"/>
+      <x:c r="C12" s="17"/>
+      <x:c r="D12"/>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="17" t="str">
@@ -3536,7 +4260,8 @@
       <x:c r="B13" s="17" t="str">
         <x:v>Record recipient, information available, accept, reject, modify, ignore, escalation, rationale, workload, staffing, patient condition, and capacity.</x:v>
       </x:c>
-      <x:c r="C13" s="17" t="str"/>
+      <x:c r="C13" s="17"/>
+      <x:c r="D13"/>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="17" t="str">
@@ -3545,7 +4270,8 @@
       <x:c r="B14" s="17" t="str">
         <x:v>Record patient and service protection, containment, notification, restriction, pause, rollback, and fallback.</x:v>
       </x:c>
-      <x:c r="C14" s="17" t="str"/>
+      <x:c r="C14" s="17"/>
+      <x:c r="D14"/>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="17" t="str">
@@ -3554,7 +4280,8 @@
       <x:c r="B15" s="17" t="str">
         <x:v>Distinguish confirmed, contributing, and unresolved technical, clinical, workflow, organizational, and governance causes.</x:v>
       </x:c>
-      <x:c r="C15" s="17" t="str"/>
+      <x:c r="C15" s="17"/>
+      <x:c r="D15"/>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="17" t="str">
@@ -3563,7 +4290,8 @@
       <x:c r="B16" s="17" t="str">
         <x:v>Record action, owner, deadline, revalidation, communication, vendor or contract response, monitoring change, and effectiveness check.</x:v>
       </x:c>
-      <x:c r="C16" s="17" t="str"/>
+      <x:c r="C16" s="17"/>
+      <x:c r="D16"/>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="17" t="str">
@@ -3572,15 +4300,17 @@
       <x:c r="B17" s="17" t="str">
         <x:v>Record closure authority, evidence, affected records and people, residual risk, recurrence prevention, and portfolio implications.</x:v>
       </x:c>
-      <x:c r="C17" s="17" t="str"/>
+      <x:c r="C17" s="17"/>
+      <x:c r="D17"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:F1"/>
+    <x:mergeCell ref="A1:D1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6d1d897ad9304621"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc51055b81a8143db"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3595,23 +4325,29 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="29" t="str">
+      <x:c r="A1" s="78" t="str">
         <x:v>AIHE-D05 — Change-Control and Renewal Record</x:v>
       </x:c>
-      <x:c r="B1" s="29"/>
-      <x:c r="C1" s="29"/>
-      <x:c r="D1" s="29"/>
+      <x:c r="B1" s="78"/>
+      <x:c r="C1" s="78"/>
+      <x:c r="D1" s="78"/>
       <x:c r="E1" s="29"/>
       <x:c r="F1" s="29"/>
     </x:row>
+    <x:row r="2">
+      <x:c r="A2"/>
+      <x:c r="B2"/>
+      <x:c r="C2"/>
+      <x:c r="D2"/>
+    </x:row>
     <x:row r="3">
-      <x:c r="A3" s="33" t="str">
+      <x:c r="A3" s="80" t="str">
         <x:v>Primary chapter</x:v>
       </x:c>
       <x:c r="B3" s="17" t="str">
         <x:v>12 — Decision Architecture and Lifecycle Governance</x:v>
       </x:c>
-      <x:c r="C3" s="33" t="str">
+      <x:c r="C3" s="80" t="str">
         <x:v>Release</x:v>
       </x:c>
       <x:c r="D3" s="17" t="str">
@@ -3619,13 +4355,13 @@
       </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="33" t="str">
+      <x:c r="A4" s="80" t="str">
         <x:v>Purpose</x:v>
       </x:c>
       <x:c r="B4" s="17" t="str">
         <x:v>Assess material changes and periodic renewal across system, data, workflow, vendor, price, law, evidence, alternatives, and exit.</x:v>
       </x:c>
-      <x:c r="C4" s="33" t="str">
+      <x:c r="C4" s="80" t="str">
         <x:v>Reader level</x:v>
       </x:c>
       <x:c r="D4" s="17" t="str">
@@ -3633,13 +4369,13 @@
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="33" t="str">
+      <x:c r="A5" s="80" t="str">
         <x:v>Required inputs</x:v>
       </x:c>
       <x:c r="B5" s="17" t="str">
         <x:v>Defined decision problem, realistic comparator, local evidence, named owners, and applicable institutional requirements</x:v>
       </x:c>
-      <x:c r="C5" s="33" t="str">
+      <x:c r="C5" s="80" t="str">
         <x:v>Expected output</x:v>
       </x:c>
       <x:c r="D5" s="17" t="str">
@@ -3660,6 +4396,12 @@
         <x:v>60–180 minutes</x:v>
       </x:c>
     </x:row>
+    <x:row r="7">
+      <x:c r="A7"/>
+      <x:c r="B7"/>
+      <x:c r="C7"/>
+      <x:c r="D7"/>
+    </x:row>
     <x:row r="8">
       <x:c r="A8" s="23" t="str">
         <x:v>Field</x:v>
@@ -3670,6 +4412,7 @@
       <x:c r="C8" s="23" t="str">
         <x:v>Institutional response</x:v>
       </x:c>
+      <x:c r="D8"/>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="17" t="str">
@@ -3678,7 +4421,8 @@
       <x:c r="B9" s="17" t="str">
         <x:v>Model, software, data, threshold, interface, intended use, population, workflow, provider, subprocessor, hosting, price, law, evidence, or alternative.</x:v>
       </x:c>
-      <x:c r="C9" s="17" t="str"/>
+      <x:c r="C9" s="17"/>
+      <x:c r="D9"/>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="17" t="str">
@@ -3687,7 +4431,8 @@
       <x:c r="B10" s="17" t="str">
         <x:v>Identify evidence, validation, economics, quality, accreditation, governance, contract, training, communication, and monitoring records requiring revision.</x:v>
       </x:c>
-      <x:c r="C10" s="17" t="str"/>
+      <x:c r="C10" s="17"/>
+      <x:c r="D10"/>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="17" t="str">
@@ -3696,7 +4441,8 @@
       <x:c r="B11" s="17" t="str">
         <x:v>Classify minor, moderate, or major; record restriction, silent mode, rollback, or pause where required.</x:v>
       </x:c>
-      <x:c r="C11" s="17" t="str"/>
+      <x:c r="C11" s="17"/>
+      <x:c r="D11"/>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="17" t="str">
@@ -3705,7 +4451,8 @@
       <x:c r="B12" s="17" t="str">
         <x:v>Define tests, subgroups, human factors, pilot, training, acceptance thresholds, approval, and release plan.</x:v>
       </x:c>
-      <x:c r="C12" s="17" t="str"/>
+      <x:c r="C12" s="17"/>
+      <x:c r="D12"/>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="17" t="str">
@@ -3714,7 +4461,8 @@
       <x:c r="B13" s="17" t="str">
         <x:v>Reassess lifecycle cost, benefit realization, budget impact, risks, alternatives, and opportunity cost.</x:v>
       </x:c>
-      <x:c r="C13" s="17" t="str"/>
+      <x:c r="C13" s="17"/>
+      <x:c r="D13"/>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="17" t="str">
@@ -3723,7 +4471,8 @@
       <x:c r="B14" s="17" t="str">
         <x:v>Continue, continue with conditions, update, restrict, pause, restart, replace, or retire.</x:v>
       </x:c>
-      <x:c r="C14" s="17" t="str"/>
+      <x:c r="C14" s="17"/>
+      <x:c r="D14"/>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="17" t="str">
@@ -3732,7 +4481,8 @@
       <x:c r="B15" s="17" t="str">
         <x:v>Record fallback, data export, retention and deletion, workflow restoration, staff and patient communication, contract termination, and physical disposition.</x:v>
       </x:c>
-      <x:c r="C15" s="17" t="str"/>
+      <x:c r="C15" s="17"/>
+      <x:c r="D15"/>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="17" t="str">
@@ -3741,15 +4491,17 @@
       <x:c r="B16" s="17" t="str">
         <x:v>Record accountable decision-maker, dissent, conditions, date, evidence cut-off, and next trigger.</x:v>
       </x:c>
-      <x:c r="C16" s="17" t="str"/>
+      <x:c r="C16" s="17"/>
+      <x:c r="D16"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:F1"/>
+    <x:mergeCell ref="A1:D1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R01442612c82c40f6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4aadc5ff4fc94e1f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3765,23 +4517,29 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="29" t="str">
+      <x:c r="A1" s="78" t="str">
         <x:v>AIHE-E01 — Circular-Economy and Sustainable-AI Assessment</x:v>
       </x:c>
-      <x:c r="B1" s="29"/>
-      <x:c r="C1" s="29"/>
-      <x:c r="D1" s="29"/>
+      <x:c r="B1" s="78"/>
+      <x:c r="C1" s="78"/>
+      <x:c r="D1" s="78"/>
       <x:c r="E1" s="29"/>
       <x:c r="F1" s="29"/>
     </x:row>
+    <x:row r="2">
+      <x:c r="A2"/>
+      <x:c r="B2"/>
+      <x:c r="C2"/>
+      <x:c r="D2"/>
+    </x:row>
     <x:row r="3">
-      <x:c r="A3" s="33" t="str">
+      <x:c r="A3" s="80" t="str">
         <x:v>Primary chapter</x:v>
       </x:c>
       <x:c r="B3" s="17" t="str">
         <x:v>13 — Circular Health Systems and Resource Stewardship</x:v>
       </x:c>
-      <x:c r="C3" s="33" t="str">
+      <x:c r="C3" s="80" t="str">
         <x:v>Release</x:v>
       </x:c>
       <x:c r="D3" s="17" t="str">
@@ -3789,13 +4547,13 @@
       </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="33" t="str">
+      <x:c r="A4" s="80" t="str">
         <x:v>Purpose</x:v>
       </x:c>
       <x:c r="B4" s="17" t="str">
         <x:v>Apply the circularity hierarchy from prevention and reduction through sharing, maintenance, reuse, refurbishment, recovery, and disposal.</x:v>
       </x:c>
-      <x:c r="C4" s="33" t="str">
+      <x:c r="C4" s="80" t="str">
         <x:v>Reader level</x:v>
       </x:c>
       <x:c r="D4" s="17" t="str">
@@ -3803,13 +4561,13 @@
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="33" t="str">
+      <x:c r="A5" s="80" t="str">
         <x:v>Required inputs</x:v>
       </x:c>
       <x:c r="B5" s="17" t="str">
         <x:v>Defined decision problem, realistic comparator, local evidence, named owners, and applicable institutional requirements</x:v>
       </x:c>
-      <x:c r="C5" s="33" t="str">
+      <x:c r="C5" s="80" t="str">
         <x:v>Expected output</x:v>
       </x:c>
       <x:c r="D5" s="17" t="str">
@@ -3830,6 +4588,12 @@
         <x:v>60–180 minutes</x:v>
       </x:c>
     </x:row>
+    <x:row r="7">
+      <x:c r="A7"/>
+      <x:c r="B7"/>
+      <x:c r="C7"/>
+      <x:c r="D7"/>
+    </x:row>
     <x:row r="8">
       <x:c r="A8" s="23" t="str">
         <x:v>Strategy or domain</x:v>
@@ -3851,8 +4615,8 @@
       <x:c r="B9" s="17" t="str">
         <x:v>Can the service need be met without new acquisition, unnecessary computation, duplicate data, or low-value activity?</x:v>
       </x:c>
-      <x:c r="C9" s="17" t="str"/>
-      <x:c r="D9" s="17" t="str"/>
+      <x:c r="C9" s="17"/>
+      <x:c r="D9" s="17"/>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="17" t="str">
@@ -3861,8 +4625,8 @@
       <x:c r="B10" s="17" t="str">
         <x:v>Can model, storage, data, hardware, energy, water, and material intensity be reduced per useful output?</x:v>
       </x:c>
-      <x:c r="C10" s="17" t="str"/>
-      <x:c r="D10" s="17" t="str"/>
+      <x:c r="C10" s="17"/>
+      <x:c r="D10" s="17"/>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="17" t="str">
@@ -3871,8 +4635,8 @@
       <x:c r="B11" s="17" t="str">
         <x:v>Can infrastructure, services, capacity, or assets be shared without unacceptable dependency or access effects?</x:v>
       </x:c>
-      <x:c r="C11" s="17" t="str"/>
-      <x:c r="D11" s="17" t="str"/>
+      <x:c r="C11" s="17"/>
+      <x:c r="D11" s="17"/>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="17" t="str">
@@ -3881,8 +4645,8 @@
       <x:c r="B12" s="17" t="str">
         <x:v>Can preventive maintenance, software support, components, and repair preserve safe useful life?</x:v>
       </x:c>
-      <x:c r="C12" s="17" t="str"/>
-      <x:c r="D12" s="17" t="str"/>
+      <x:c r="C12" s="17"/>
+      <x:c r="D12" s="17"/>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="17" t="str">
@@ -3891,8 +4655,8 @@
       <x:c r="B13" s="17" t="str">
         <x:v>Can the asset or component serve a verified use after data erasure, validation, and recipient due diligence?</x:v>
       </x:c>
-      <x:c r="C13" s="17" t="str"/>
-      <x:c r="D13" s="17" t="str"/>
+      <x:c r="C13" s="17"/>
+      <x:c r="D13" s="17"/>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="17" t="str">
@@ -3901,8 +4665,8 @@
       <x:c r="B14" s="17" t="str">
         <x:v>Can selected components and controls restore performance and evidence at lower lifecycle burden?</x:v>
       </x:c>
-      <x:c r="C14" s="17" t="str"/>
-      <x:c r="D14" s="17" t="str"/>
+      <x:c r="C14" s="17"/>
+      <x:c r="D14" s="17"/>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="17" t="str">
@@ -3911,8 +4675,8 @@
       <x:c r="B15" s="17" t="str">
         <x:v>Are take-back, traceability, verified recovery, and critical-material outcomes documented?</x:v>
       </x:c>
-      <x:c r="C15" s="17" t="str"/>
-      <x:c r="D15" s="17" t="str"/>
+      <x:c r="C15" s="17"/>
+      <x:c r="D15" s="17"/>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="17" t="str">
@@ -3921,8 +4685,8 @@
       <x:c r="B16" s="17" t="str">
         <x:v>Is final disposal necessary, lawful, secure, and supported by chain of custody?</x:v>
       </x:c>
-      <x:c r="C16" s="17" t="str"/>
-      <x:c r="D16" s="17" t="str"/>
+      <x:c r="C16" s="17"/>
+      <x:c r="D16" s="17"/>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="17" t="str">
@@ -3931,16 +4695,17 @@
       <x:c r="B17" s="17" t="str">
         <x:v>Could lower unit cost or greater capacity increase total use or shift burden across places, groups, or lifecycle stages?</x:v>
       </x:c>
-      <x:c r="C17" s="17" t="str"/>
-      <x:c r="D17" s="17" t="str"/>
+      <x:c r="C17" s="17"/>
+      <x:c r="D17" s="17"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:F1"/>
+    <x:mergeCell ref="A1:D1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4415a7db8a7640ba"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb664a670de614691"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3958,56 +4723,70 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="29" t="str">
+      <x:c r="A1" s="78" t="str">
         <x:v>AIHE-E02 — Circular Procurement and Supplier Scorecard</x:v>
       </x:c>
-      <x:c r="B1" s="29"/>
-      <x:c r="C1" s="29"/>
-      <x:c r="D1" s="29"/>
-      <x:c r="E1" s="29"/>
-      <x:c r="F1" s="29"/>
+      <x:c r="B1" s="78"/>
+      <x:c r="C1" s="78"/>
+      <x:c r="D1" s="78"/>
+      <x:c r="E1" s="78"/>
+      <x:c r="F1" s="78"/>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2"/>
+      <x:c r="B2"/>
+      <x:c r="C2"/>
+      <x:c r="D2"/>
+      <x:c r="E2"/>
+      <x:c r="F2"/>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="33" t="str">
+      <x:c r="A3" s="80" t="str">
         <x:v>Primary chapter</x:v>
       </x:c>
       <x:c r="B3" s="17" t="str">
         <x:v>14 — Circular Procurement and Asset Stewardship</x:v>
       </x:c>
-      <x:c r="C3" s="33" t="str">
+      <x:c r="C3" s="80" t="str">
         <x:v>Release</x:v>
       </x:c>
       <x:c r="D3" s="17" t="str">
         <x:v>V1.0</x:v>
       </x:c>
+      <x:c r="E3"/>
+      <x:c r="F3"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="33" t="str">
+      <x:c r="A4" s="80" t="str">
         <x:v>Purpose</x:v>
       </x:c>
       <x:c r="B4" s="17" t="str">
         <x:v>Evaluate durability, modularity, repairability, interoperability, resource information, take-back, pricing, residual value, and exit.</x:v>
       </x:c>
-      <x:c r="C4" s="33" t="str">
+      <x:c r="C4" s="80" t="str">
         <x:v>Reader level</x:v>
       </x:c>
       <x:c r="D4" s="17" t="str">
         <x:v>Applied</x:v>
       </x:c>
+      <x:c r="E4"/>
+      <x:c r="F4"/>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="33" t="str">
+      <x:c r="A5" s="80" t="str">
         <x:v>Required inputs</x:v>
       </x:c>
       <x:c r="B5" s="17" t="str">
         <x:v>Defined decision problem, realistic comparator, local evidence, named owners, and applicable institutional requirements</x:v>
       </x:c>
-      <x:c r="C5" s="33" t="str">
+      <x:c r="C5" s="80" t="str">
         <x:v>Expected output</x:v>
       </x:c>
       <x:c r="D5" s="17" t="str">
         <x:v>Versioned institutional decision record with conditions, monitoring, review date, and exit route</x:v>
       </x:c>
+      <x:c r="E5"/>
+      <x:c r="F5"/>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="33" t="str">
@@ -4022,6 +4801,16 @@
       <x:c r="D6" s="17" t="str">
         <x:v>60–180 minutes</x:v>
       </x:c>
+      <x:c r="E6"/>
+      <x:c r="F6"/>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7"/>
+      <x:c r="B7"/>
+      <x:c r="C7"/>
+      <x:c r="D7"/>
+      <x:c r="E7"/>
+      <x:c r="F7"/>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="23" t="str">
@@ -4047,91 +4836,91 @@
       <x:c r="A9" s="17" t="str">
         <x:v>Durability and supported life</x:v>
       </x:c>
-      <x:c r="B9" s="17" t="str"/>
-      <x:c r="C9" s="17" t="str"/>
-      <x:c r="D9" s="17" t="str"/>
-      <x:c r="E9" s="17" t="str"/>
-      <x:c r="F9" s="17" t="str"/>
+      <x:c r="B9" s="17"/>
+      <x:c r="C9" s="17"/>
+      <x:c r="D9" s="17"/>
+      <x:c r="E9" s="17"/>
+      <x:c r="F9" s="17"/>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="17" t="str">
         <x:v>Modularity, upgradeability, and component availability</x:v>
       </x:c>
-      <x:c r="B10" s="17" t="str"/>
-      <x:c r="C10" s="17" t="str"/>
-      <x:c r="D10" s="17" t="str"/>
-      <x:c r="E10" s="17" t="str"/>
-      <x:c r="F10" s="17" t="str"/>
+      <x:c r="B10" s="17"/>
+      <x:c r="C10" s="17"/>
+      <x:c r="D10" s="17"/>
+      <x:c r="E10" s="17"/>
+      <x:c r="F10" s="17"/>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="17" t="str">
         <x:v>Repairability and maintenance information</x:v>
       </x:c>
-      <x:c r="B11" s="17" t="str"/>
-      <x:c r="C11" s="17" t="str"/>
-      <x:c r="D11" s="17" t="str"/>
-      <x:c r="E11" s="17" t="str"/>
-      <x:c r="F11" s="17" t="str"/>
+      <x:c r="B11" s="17"/>
+      <x:c r="C11" s="17"/>
+      <x:c r="D11" s="17"/>
+      <x:c r="E11" s="17"/>
+      <x:c r="F11" s="17"/>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="17" t="str">
         <x:v>Interoperability, portability, and avoidance of lock-in</x:v>
       </x:c>
-      <x:c r="B12" s="17" t="str"/>
-      <x:c r="C12" s="17" t="str"/>
-      <x:c r="D12" s="17" t="str"/>
-      <x:c r="E12" s="17" t="str"/>
-      <x:c r="F12" s="17" t="str"/>
+      <x:c r="B12" s="17"/>
+      <x:c r="C12" s="17"/>
+      <x:c r="D12" s="17"/>
+      <x:c r="E12" s="17"/>
+      <x:c r="F12" s="17"/>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="17" t="str">
         <x:v>Energy, water, carbon, material, and utilization information</x:v>
       </x:c>
-      <x:c r="B13" s="17" t="str"/>
-      <x:c r="C13" s="17" t="str"/>
-      <x:c r="D13" s="17" t="str"/>
-      <x:c r="E13" s="17" t="str"/>
-      <x:c r="F13" s="17" t="str"/>
+      <x:c r="B13" s="17"/>
+      <x:c r="C13" s="17"/>
+      <x:c r="D13" s="17"/>
+      <x:c r="E13" s="17"/>
+      <x:c r="F13" s="17"/>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="17" t="str">
         <x:v>Product circularity, provenance, and recovery information</x:v>
       </x:c>
-      <x:c r="B14" s="17" t="str"/>
-      <x:c r="C14" s="17" t="str"/>
-      <x:c r="D14" s="17" t="str"/>
-      <x:c r="E14" s="17" t="str"/>
-      <x:c r="F14" s="17" t="str"/>
+      <x:c r="B14" s="17"/>
+      <x:c r="C14" s="17"/>
+      <x:c r="D14" s="17"/>
+      <x:c r="E14" s="17"/>
+      <x:c r="F14" s="17"/>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="17" t="str">
         <x:v>Take-back, refurbishment, remanufacture, and recovery</x:v>
       </x:c>
-      <x:c r="B15" s="17" t="str"/>
-      <x:c r="C15" s="17" t="str"/>
-      <x:c r="D15" s="17" t="str"/>
-      <x:c r="E15" s="17" t="str"/>
-      <x:c r="F15" s="17" t="str"/>
+      <x:c r="B15" s="17"/>
+      <x:c r="C15" s="17"/>
+      <x:c r="D15" s="17"/>
+      <x:c r="E15" s="17"/>
+      <x:c r="F15" s="17"/>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="17" t="str">
         <x:v>Secure erasure, chain of custody, and disposition evidence</x:v>
       </x:c>
-      <x:c r="B16" s="17" t="str"/>
-      <x:c r="C16" s="17" t="str"/>
-      <x:c r="D16" s="17" t="str"/>
-      <x:c r="E16" s="17" t="str"/>
-      <x:c r="F16" s="17" t="str"/>
+      <x:c r="B16" s="17"/>
+      <x:c r="C16" s="17"/>
+      <x:c r="D16" s="17"/>
+      <x:c r="E16" s="17"/>
+      <x:c r="F16" s="17"/>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="17" t="str">
         <x:v>Pricing, residual value, risk sharing, and exit</x:v>
       </x:c>
-      <x:c r="B17" s="17" t="str"/>
-      <x:c r="C17" s="17" t="str"/>
-      <x:c r="D17" s="17" t="str"/>
-      <x:c r="E17" s="17" t="str"/>
-      <x:c r="F17" s="17" t="str"/>
+      <x:c r="B17" s="17"/>
+      <x:c r="C17" s="17"/>
+      <x:c r="D17" s="17"/>
+      <x:c r="E17" s="17"/>
+      <x:c r="F17" s="17"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -4139,7 +4928,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R312808655c034ad2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc7b72bec19b346ed"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4157,56 +4946,70 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="29" t="str">
+      <x:c r="A1" s="78" t="str">
         <x:v>AIHE-E03 — Asset-Life Decision Record</x:v>
       </x:c>
-      <x:c r="B1" s="29"/>
-      <x:c r="C1" s="29"/>
-      <x:c r="D1" s="29"/>
-      <x:c r="E1" s="29"/>
-      <x:c r="F1" s="29"/>
+      <x:c r="B1" s="78"/>
+      <x:c r="C1" s="78"/>
+      <x:c r="D1" s="78"/>
+      <x:c r="E1" s="78"/>
+      <x:c r="F1" s="78"/>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2"/>
+      <x:c r="B2"/>
+      <x:c r="C2"/>
+      <x:c r="D2"/>
+      <x:c r="E2"/>
+      <x:c r="F2"/>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="33" t="str">
+      <x:c r="A3" s="80" t="str">
         <x:v>Primary chapter</x:v>
       </x:c>
       <x:c r="B3" s="17" t="str">
         <x:v>14 — Circular Procurement and Asset Stewardship</x:v>
       </x:c>
-      <x:c r="C3" s="33" t="str">
+      <x:c r="C3" s="80" t="str">
         <x:v>Release</x:v>
       </x:c>
       <x:c r="D3" s="17" t="str">
         <x:v>V1.0</x:v>
       </x:c>
+      <x:c r="E3"/>
+      <x:c r="F3"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="33" t="str">
+      <x:c r="A4" s="80" t="str">
         <x:v>Purpose</x:v>
       </x:c>
       <x:c r="B4" s="17" t="str">
         <x:v>Compare maintain, refurbish, replace, and shared-service options across suitability, life, cost, resources, resilience, and disposition.</x:v>
       </x:c>
-      <x:c r="C4" s="33" t="str">
+      <x:c r="C4" s="80" t="str">
         <x:v>Reader level</x:v>
       </x:c>
       <x:c r="D4" s="17" t="str">
         <x:v>Applied</x:v>
       </x:c>
+      <x:c r="E4"/>
+      <x:c r="F4"/>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="33" t="str">
+      <x:c r="A5" s="80" t="str">
         <x:v>Required inputs</x:v>
       </x:c>
       <x:c r="B5" s="17" t="str">
         <x:v>Defined decision problem, realistic comparator, local evidence, named owners, and applicable institutional requirements</x:v>
       </x:c>
-      <x:c r="C5" s="33" t="str">
+      <x:c r="C5" s="80" t="str">
         <x:v>Expected output</x:v>
       </x:c>
       <x:c r="D5" s="17" t="str">
         <x:v>Versioned institutional decision record with conditions, monitoring, review date, and exit route</x:v>
       </x:c>
+      <x:c r="E5"/>
+      <x:c r="F5"/>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="33" t="str">
@@ -4221,6 +5024,16 @@
       <x:c r="D6" s="17" t="str">
         <x:v>60–180 minutes</x:v>
       </x:c>
+      <x:c r="E6"/>
+      <x:c r="F6"/>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7"/>
+      <x:c r="B7"/>
+      <x:c r="C7"/>
+      <x:c r="D7"/>
+      <x:c r="E7"/>
+      <x:c r="F7"/>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="23" t="str">
@@ -4246,91 +5059,91 @@
       <x:c r="A9" s="17" t="str">
         <x:v>Clinical and technical suitability</x:v>
       </x:c>
-      <x:c r="B9" s="17" t="str"/>
-      <x:c r="C9" s="17" t="str"/>
-      <x:c r="D9" s="17" t="str"/>
-      <x:c r="E9" s="17" t="str"/>
-      <x:c r="F9" s="17" t="str"/>
+      <x:c r="B9" s="17"/>
+      <x:c r="C9" s="17"/>
+      <x:c r="D9" s="17"/>
+      <x:c r="E9" s="17"/>
+      <x:c r="F9" s="17"/>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="17" t="str">
         <x:v>Remaining useful life and reliability</x:v>
       </x:c>
-      <x:c r="B10" s="17" t="str"/>
-      <x:c r="C10" s="17" t="str"/>
-      <x:c r="D10" s="17" t="str"/>
-      <x:c r="E10" s="17" t="str"/>
-      <x:c r="F10" s="17" t="str"/>
+      <x:c r="B10" s="17"/>
+      <x:c r="C10" s="17"/>
+      <x:c r="D10" s="17"/>
+      <x:c r="E10" s="17"/>
+      <x:c r="F10" s="17"/>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="17" t="str">
         <x:v>Validation and regulatory burden</x:v>
       </x:c>
-      <x:c r="B11" s="17" t="str"/>
-      <x:c r="C11" s="17" t="str"/>
-      <x:c r="D11" s="17" t="str"/>
-      <x:c r="E11" s="17" t="str"/>
-      <x:c r="F11" s="17" t="str"/>
+      <x:c r="B11" s="17"/>
+      <x:c r="C11" s="17"/>
+      <x:c r="D11" s="17"/>
+      <x:c r="E11" s="17"/>
+      <x:c r="F11" s="17"/>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="17" t="str">
         <x:v>Lifecycle cost and price exposure</x:v>
       </x:c>
-      <x:c r="B12" s="17" t="str"/>
-      <x:c r="C12" s="17" t="str"/>
-      <x:c r="D12" s="17" t="str"/>
-      <x:c r="E12" s="17" t="str"/>
-      <x:c r="F12" s="17" t="str"/>
+      <x:c r="B12" s="17"/>
+      <x:c r="C12" s="17"/>
+      <x:c r="D12" s="17"/>
+      <x:c r="E12" s="17"/>
+      <x:c r="F12" s="17"/>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="17" t="str">
         <x:v>Energy, water, material, and waste effects</x:v>
       </x:c>
-      <x:c r="B13" s="17" t="str"/>
-      <x:c r="C13" s="17" t="str"/>
-      <x:c r="D13" s="17" t="str"/>
-      <x:c r="E13" s="17" t="str"/>
-      <x:c r="F13" s="17" t="str"/>
+      <x:c r="B13" s="17"/>
+      <x:c r="C13" s="17"/>
+      <x:c r="D13" s="17"/>
+      <x:c r="E13" s="17"/>
+      <x:c r="F13" s="17"/>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="17" t="str">
         <x:v>Software, cybersecurity, and interoperability</x:v>
       </x:c>
-      <x:c r="B14" s="17" t="str"/>
-      <x:c r="C14" s="17" t="str"/>
-      <x:c r="D14" s="17" t="str"/>
-      <x:c r="E14" s="17" t="str"/>
-      <x:c r="F14" s="17" t="str"/>
+      <x:c r="B14" s="17"/>
+      <x:c r="C14" s="17"/>
+      <x:c r="D14" s="17"/>
+      <x:c r="E14" s="17"/>
+      <x:c r="F14" s="17"/>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="17" t="str">
         <x:v>Workforce, workflow, downtime, and transition</x:v>
       </x:c>
-      <x:c r="B15" s="17" t="str"/>
-      <x:c r="C15" s="17" t="str"/>
-      <x:c r="D15" s="17" t="str"/>
-      <x:c r="E15" s="17" t="str"/>
-      <x:c r="F15" s="17" t="str"/>
+      <x:c r="B15" s="17"/>
+      <x:c r="C15" s="17"/>
+      <x:c r="D15" s="17"/>
+      <x:c r="E15" s="17"/>
+      <x:c r="F15" s="17"/>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="17" t="str">
         <x:v>Resilience, dependency, and exit</x:v>
       </x:c>
-      <x:c r="B16" s="17" t="str"/>
-      <x:c r="C16" s="17" t="str"/>
-      <x:c r="D16" s="17" t="str"/>
-      <x:c r="E16" s="17" t="str"/>
-      <x:c r="F16" s="17" t="str"/>
+      <x:c r="B16" s="17"/>
+      <x:c r="C16" s="17"/>
+      <x:c r="D16" s="17"/>
+      <x:c r="E16" s="17"/>
+      <x:c r="F16" s="17"/>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="17" t="str">
         <x:v>Residual value and final disposition</x:v>
       </x:c>
-      <x:c r="B17" s="17" t="str"/>
-      <x:c r="C17" s="17" t="str"/>
-      <x:c r="D17" s="17" t="str"/>
-      <x:c r="E17" s="17" t="str"/>
-      <x:c r="F17" s="17" t="str"/>
+      <x:c r="B17" s="17"/>
+      <x:c r="C17" s="17"/>
+      <x:c r="D17" s="17"/>
+      <x:c r="E17" s="17"/>
+      <x:c r="F17" s="17"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -4338,7 +5151,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0d74aef212b94c56"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1f3412b26c0249c2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4353,23 +5166,29 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="29" t="str">
+      <x:c r="A1" s="78" t="str">
         <x:v>AIHE-E04 — Circularity-Adjusted Evaluation Record</x:v>
       </x:c>
-      <x:c r="B1" s="29"/>
-      <x:c r="C1" s="29"/>
-      <x:c r="D1" s="29"/>
+      <x:c r="B1" s="78"/>
+      <x:c r="C1" s="78"/>
+      <x:c r="D1" s="78"/>
       <x:c r="E1" s="29"/>
       <x:c r="F1" s="29"/>
     </x:row>
+    <x:row r="2">
+      <x:c r="A2"/>
+      <x:c r="B2"/>
+      <x:c r="C2"/>
+      <x:c r="D2"/>
+    </x:row>
     <x:row r="3">
-      <x:c r="A3" s="33" t="str">
+      <x:c r="A3" s="80" t="str">
         <x:v>Primary chapter</x:v>
       </x:c>
       <x:c r="B3" s="17" t="str">
         <x:v>15 — Circularity-Adjusted Evaluation and Sustainable Value</x:v>
       </x:c>
-      <x:c r="C3" s="33" t="str">
+      <x:c r="C3" s="80" t="str">
         <x:v>Release</x:v>
       </x:c>
       <x:c r="D3" s="17" t="str">
@@ -4377,13 +5196,13 @@
       </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="33" t="str">
+      <x:c r="A4" s="80" t="str">
         <x:v>Purpose</x:v>
       </x:c>
       <x:c r="B4" s="17" t="str">
         <x:v>Extend conventional economic evaluation with environmental, material, residual-value, resilience, equity, rebound, and burden evidence.</x:v>
       </x:c>
-      <x:c r="C4" s="33" t="str">
+      <x:c r="C4" s="80" t="str">
         <x:v>Reader level</x:v>
       </x:c>
       <x:c r="D4" s="17" t="str">
@@ -4391,13 +5210,13 @@
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="33" t="str">
+      <x:c r="A5" s="80" t="str">
         <x:v>Required inputs</x:v>
       </x:c>
       <x:c r="B5" s="17" t="str">
         <x:v>Defined decision problem, realistic comparator, local evidence, named owners, and applicable institutional requirements</x:v>
       </x:c>
-      <x:c r="C5" s="33" t="str">
+      <x:c r="C5" s="80" t="str">
         <x:v>Expected output</x:v>
       </x:c>
       <x:c r="D5" s="17" t="str">
@@ -4418,6 +5237,12 @@
         <x:v>60–180 minutes</x:v>
       </x:c>
     </x:row>
+    <x:row r="7">
+      <x:c r="A7"/>
+      <x:c r="B7"/>
+      <x:c r="C7"/>
+      <x:c r="D7"/>
+    </x:row>
     <x:row r="8">
       <x:c r="A8" s="23" t="str">
         <x:v>Field</x:v>
@@ -4428,6 +5253,7 @@
       <x:c r="C8" s="23" t="str">
         <x:v>Institutional response</x:v>
       </x:c>
+      <x:c r="D8"/>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="17" t="str">
@@ -4436,7 +5262,8 @@
       <x:c r="B9" s="17" t="str">
         <x:v>Define the service delivered, population, quality level, volume, and time horizon.</x:v>
       </x:c>
-      <x:c r="C9" s="17" t="str"/>
+      <x:c r="C9" s="17"/>
+      <x:c r="D9"/>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="17" t="str">
@@ -4445,7 +5272,8 @@
       <x:c r="B10" s="17" t="str">
         <x:v>Specify model, data, compute, network, devices, supporting equipment, maintenance, replacement, transport, and disposition included.</x:v>
       </x:c>
-      <x:c r="C10" s="17" t="str"/>
+      <x:c r="C10" s="17"/>
+      <x:c r="D10"/>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="17" t="str">
@@ -4454,7 +5282,8 @@
       <x:c r="B11" s="17" t="str">
         <x:v>Report health, service, workforce, quality, and economic outcomes before circular adjustments.</x:v>
       </x:c>
-      <x:c r="C11" s="17" t="str"/>
+      <x:c r="C11" s="17"/>
+      <x:c r="D11"/>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="17" t="str">
@@ -4463,7 +5292,8 @@
       <x:c r="B12" s="17" t="str">
         <x:v>Report energy, water, carbon, virgin and recovered material, waste, and critical dependencies per functional unit.</x:v>
       </x:c>
-      <x:c r="C12" s="17" t="str"/>
+      <x:c r="C12" s="17"/>
+      <x:c r="D12"/>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="17" t="str">
@@ -4472,7 +5302,8 @@
       <x:c r="B13" s="17" t="str">
         <x:v>Record useful remaining life, resale, redeployment, take-back, recovery credit, and realization cost.</x:v>
       </x:c>
-      <x:c r="C13" s="17" t="str"/>
+      <x:c r="C13" s="17"/>
+      <x:c r="D13"/>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="17" t="str">
@@ -4481,7 +5312,8 @@
       <x:c r="B14" s="17" t="str">
         <x:v>Record redundancy, availability, lead time, dependency, repair capacity, and continuity effects.</x:v>
       </x:c>
-      <x:c r="C14" s="17" t="str"/>
+      <x:c r="C14" s="17"/>
+      <x:c r="D14"/>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="17" t="str">
@@ -4490,7 +5322,8 @@
       <x:c r="B15" s="17" t="str">
         <x:v>Identify who benefits, who bears environmental and labor burdens, and which regions or groups are affected.</x:v>
       </x:c>
-      <x:c r="C15" s="17" t="str"/>
+      <x:c r="C15" s="17"/>
+      <x:c r="D15"/>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="17" t="str">
@@ -4499,7 +5332,8 @@
       <x:c r="B16" s="17" t="str">
         <x:v>Explain which effects are monetized, which remain disaggregated, valuation sources, and overlap with conventional costs or outcomes.</x:v>
       </x:c>
-      <x:c r="C16" s="17" t="str"/>
+      <x:c r="C16" s="17"/>
+      <x:c r="D16"/>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="17" t="str">
@@ -4508,7 +5342,8 @@
       <x:c r="B17" s="17" t="str">
         <x:v>Test use, lifetime, performance, prices, disposal, recovery, environmental factors, and induced demand.</x:v>
       </x:c>
-      <x:c r="C17" s="17" t="str"/>
+      <x:c r="C17" s="17"/>
+      <x:c r="D17"/>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="17" t="str">
@@ -4517,15 +5352,17 @@
       <x:c r="B18" s="17" t="str">
         <x:v>State conventional and adjusted results, non-compensatory constraints, preferred option, conditions, and review triggers.</x:v>
       </x:c>
-      <x:c r="C18" s="17" t="str"/>
+      <x:c r="C18" s="17"/>
+      <x:c r="D18"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:F1"/>
+    <x:mergeCell ref="A1:D1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re03ce994905547d2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2d48227fe1bc401e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4542,56 +5379,66 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="29" t="str">
+      <x:c r="A1" s="78" t="str">
         <x:v>AIHE-E05 — Environmental, Circularity, and Disposition Dashboard</x:v>
       </x:c>
-      <x:c r="B1" s="29"/>
-      <x:c r="C1" s="29"/>
-      <x:c r="D1" s="29"/>
-      <x:c r="E1" s="29"/>
+      <x:c r="B1" s="78"/>
+      <x:c r="C1" s="78"/>
+      <x:c r="D1" s="78"/>
+      <x:c r="E1" s="78"/>
       <x:c r="F1" s="29"/>
     </x:row>
+    <x:row r="2">
+      <x:c r="A2"/>
+      <x:c r="B2"/>
+      <x:c r="C2"/>
+      <x:c r="D2"/>
+      <x:c r="E2"/>
+    </x:row>
     <x:row r="3">
-      <x:c r="A3" s="33" t="str">
+      <x:c r="A3" s="80" t="str">
         <x:v>Primary chapter</x:v>
       </x:c>
       <x:c r="B3" s="17" t="str">
         <x:v>15 — Circularity-Adjusted Evaluation and Sustainable Value</x:v>
       </x:c>
-      <x:c r="C3" s="33" t="str">
+      <x:c r="C3" s="80" t="str">
         <x:v>Release</x:v>
       </x:c>
       <x:c r="D3" s="17" t="str">
         <x:v>V1.0</x:v>
       </x:c>
+      <x:c r="E3"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="33" t="str">
+      <x:c r="A4" s="80" t="str">
         <x:v>Purpose</x:v>
       </x:c>
       <x:c r="B4" s="17" t="str">
         <x:v>Monitor acquisition, utilization, asset life, resource intensity, materials, take-back, recovery, rebound, resilience, and disposition.</x:v>
       </x:c>
-      <x:c r="C4" s="33" t="str">
+      <x:c r="C4" s="80" t="str">
         <x:v>Reader level</x:v>
       </x:c>
       <x:c r="D4" s="17" t="str">
         <x:v>Applied</x:v>
       </x:c>
+      <x:c r="E4"/>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="33" t="str">
+      <x:c r="A5" s="80" t="str">
         <x:v>Required inputs</x:v>
       </x:c>
       <x:c r="B5" s="17" t="str">
         <x:v>Defined decision problem, realistic comparator, local evidence, named owners, and applicable institutional requirements</x:v>
       </x:c>
-      <x:c r="C5" s="33" t="str">
+      <x:c r="C5" s="80" t="str">
         <x:v>Expected output</x:v>
       </x:c>
       <x:c r="D5" s="17" t="str">
         <x:v>Versioned institutional decision record with conditions, monitoring, review date, and exit route</x:v>
       </x:c>
+      <x:c r="E5"/>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="33" t="str">
@@ -4606,6 +5453,14 @@
       <x:c r="D6" s="17" t="str">
         <x:v>60–180 minutes</x:v>
       </x:c>
+      <x:c r="E6"/>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7"/>
+      <x:c r="B7"/>
+      <x:c r="C7"/>
+      <x:c r="D7"/>
+      <x:c r="E7"/>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="23" t="str">
@@ -4628,81 +5483,82 @@
       <x:c r="A9" s="17" t="str">
         <x:v>Avoided or deferred acquisition</x:v>
       </x:c>
-      <x:c r="B9" s="17" t="str"/>
-      <x:c r="C9" s="17" t="str"/>
-      <x:c r="D9" s="17" t="str"/>
-      <x:c r="E9" s="17" t="str"/>
+      <x:c r="B9" s="17"/>
+      <x:c r="C9" s="17"/>
+      <x:c r="D9" s="17"/>
+      <x:c r="E9" s="17"/>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="17" t="str">
         <x:v>Utilization, sharing, and useful life</x:v>
       </x:c>
-      <x:c r="B10" s="17" t="str"/>
-      <x:c r="C10" s="17" t="str"/>
-      <x:c r="D10" s="17" t="str"/>
-      <x:c r="E10" s="17" t="str"/>
+      <x:c r="B10" s="17"/>
+      <x:c r="C10" s="17"/>
+      <x:c r="D10" s="17"/>
+      <x:c r="E10" s="17"/>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="17" t="str">
         <x:v>Maintenance, repair, refurbishment, and redeployment</x:v>
       </x:c>
-      <x:c r="B11" s="17" t="str"/>
-      <x:c r="C11" s="17" t="str"/>
-      <x:c r="D11" s="17" t="str"/>
-      <x:c r="E11" s="17" t="str"/>
+      <x:c r="B11" s="17"/>
+      <x:c r="C11" s="17"/>
+      <x:c r="D11" s="17"/>
+      <x:c r="E11" s="17"/>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="17" t="str">
         <x:v>Energy, water, carbon, and data-storage intensity</x:v>
       </x:c>
-      <x:c r="B12" s="17" t="str"/>
-      <x:c r="C12" s="17" t="str"/>
-      <x:c r="D12" s="17" t="str"/>
-      <x:c r="E12" s="17" t="str"/>
+      <x:c r="B12" s="17"/>
+      <x:c r="C12" s="17"/>
+      <x:c r="D12" s="17"/>
+      <x:c r="E12" s="17"/>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="17" t="str">
         <x:v>Virgin, recovered, and critical material use</x:v>
       </x:c>
-      <x:c r="B13" s="17" t="str"/>
-      <x:c r="C13" s="17" t="str"/>
-      <x:c r="D13" s="17" t="str"/>
-      <x:c r="E13" s="17" t="str"/>
+      <x:c r="B13" s="17"/>
+      <x:c r="C13" s="17"/>
+      <x:c r="D13" s="17"/>
+      <x:c r="E13" s="17"/>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="17" t="str">
         <x:v>Verified take-back, recovery, and unverified disposition</x:v>
       </x:c>
-      <x:c r="B14" s="17" t="str"/>
-      <x:c r="C14" s="17" t="str"/>
-      <x:c r="D14" s="17" t="str"/>
-      <x:c r="E14" s="17" t="str"/>
+      <x:c r="B14" s="17"/>
+      <x:c r="C14" s="17"/>
+      <x:c r="D14" s="17"/>
+      <x:c r="E14" s="17"/>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="17" t="str">
         <x:v>Residual value and recovery cost</x:v>
       </x:c>
-      <x:c r="B15" s="17" t="str"/>
-      <x:c r="C15" s="17" t="str"/>
-      <x:c r="D15" s="17" t="str"/>
-      <x:c r="E15" s="17" t="str"/>
+      <x:c r="B15" s="17"/>
+      <x:c r="C15" s="17"/>
+      <x:c r="D15" s="17"/>
+      <x:c r="E15" s="17"/>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="17" t="str">
         <x:v>Rebound, safety, equity, resilience, and continuity</x:v>
       </x:c>
-      <x:c r="B16" s="17" t="str"/>
-      <x:c r="C16" s="17" t="str"/>
-      <x:c r="D16" s="17" t="str"/>
-      <x:c r="E16" s="17" t="str"/>
+      <x:c r="B16" s="17"/>
+      <x:c r="C16" s="17"/>
+      <x:c r="D16" s="17"/>
+      <x:c r="E16" s="17"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:F1"/>
+    <x:mergeCell ref="A1:E1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R33bb6ef75c844e31"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R68526f714b194389"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4717,23 +5573,29 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="29" t="str">
+      <x:c r="A1" s="78" t="str">
         <x:v>AIHE-A01 — Decision and Use-Case Specification</x:v>
       </x:c>
-      <x:c r="B1" s="29"/>
-      <x:c r="C1" s="29"/>
-      <x:c r="D1" s="29"/>
+      <x:c r="B1" s="78"/>
+      <x:c r="C1" s="78"/>
+      <x:c r="D1" s="78"/>
       <x:c r="E1" s="29"/>
       <x:c r="F1" s="29"/>
     </x:row>
+    <x:row r="2">
+      <x:c r="A2"/>
+      <x:c r="B2"/>
+      <x:c r="C2"/>
+      <x:c r="D2"/>
+    </x:row>
     <x:row r="3">
-      <x:c r="A3" s="33" t="str">
+      <x:c r="A3" s="80" t="str">
         <x:v>Primary chapter</x:v>
       </x:c>
       <x:c r="B3" s="17" t="str">
         <x:v>1 — AI as a Health-System Intervention</x:v>
       </x:c>
-      <x:c r="C3" s="33" t="str">
+      <x:c r="C3" s="80" t="str">
         <x:v>Release</x:v>
       </x:c>
       <x:c r="D3" s="17" t="str">
@@ -4741,13 +5603,13 @@
       </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="33" t="str">
+      <x:c r="A4" s="80" t="str">
         <x:v>Purpose</x:v>
       </x:c>
       <x:c r="B4" s="17" t="str">
         <x:v>Define the service problem, full intervention, realistic comparators, outcomes, value mechanism, decision rule, and review cycle.</x:v>
       </x:c>
-      <x:c r="C4" s="33" t="str">
+      <x:c r="C4" s="80" t="str">
         <x:v>Reader level</x:v>
       </x:c>
       <x:c r="D4" s="17" t="str">
@@ -4755,13 +5617,13 @@
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="33" t="str">
+      <x:c r="A5" s="80" t="str">
         <x:v>Required inputs</x:v>
       </x:c>
       <x:c r="B5" s="17" t="str">
         <x:v>Defined decision problem, realistic comparator, local evidence, named owners, and applicable institutional requirements</x:v>
       </x:c>
-      <x:c r="C5" s="33" t="str">
+      <x:c r="C5" s="80" t="str">
         <x:v>Expected output</x:v>
       </x:c>
       <x:c r="D5" s="17" t="str">
@@ -4782,6 +5644,12 @@
         <x:v>60–180 minutes</x:v>
       </x:c>
     </x:row>
+    <x:row r="7">
+      <x:c r="A7"/>
+      <x:c r="B7"/>
+      <x:c r="C7"/>
+      <x:c r="D7"/>
+    </x:row>
     <x:row r="8">
       <x:c r="A8" s="23" t="str">
         <x:v>Field</x:v>
@@ -4792,6 +5660,7 @@
       <x:c r="C8" s="23" t="str">
         <x:v>Institutional response</x:v>
       </x:c>
+      <x:c r="D8"/>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="17" t="str">
@@ -4800,7 +5669,8 @@
       <x:c r="B9" s="17" t="str">
         <x:v>Describe the unmet clinical, operational, workforce, quality, accreditation, or public-health need using measurable baseline evidence.</x:v>
       </x:c>
-      <x:c r="C9" s="17" t="str"/>
+      <x:c r="C9" s="17"/>
+      <x:c r="D9"/>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="17" t="str">
@@ -4809,7 +5679,8 @@
       <x:c r="B10" s="17" t="str">
         <x:v>Define included and excluded populations, services, locations, and time periods.</x:v>
       </x:c>
-      <x:c r="C10" s="17" t="str"/>
+      <x:c r="C10" s="17"/>
+      <x:c r="D10"/>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="17" t="str">
@@ -4818,7 +5689,8 @@
       <x:c r="B11" s="17" t="str">
         <x:v>Describe the complete intervention bundle: data, model, interfaces, thresholds, users, review, workflow, downstream action, monitoring, support, and exit.</x:v>
       </x:c>
-      <x:c r="C11" s="17" t="str"/>
+      <x:c r="C11" s="17"/>
+      <x:c r="D11"/>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="17" t="str">
@@ -4827,7 +5699,8 @@
       <x:c r="B12" s="17" t="str">
         <x:v>Record current practice, process redesign, staffing, equipment, conventional digital tools, alternative AI, shared service, and no-change options where relevant.</x:v>
       </x:c>
-      <x:c r="C12" s="17" t="str"/>
+      <x:c r="C12" s="17"/>
+      <x:c r="D12"/>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="17" t="str">
@@ -4836,7 +5709,8 @@
       <x:c r="B13" s="17" t="str">
         <x:v>Identify the authority making the decision and the hospital, health-system, payer, patient, societal, or combined perspective.</x:v>
       </x:c>
-      <x:c r="C13" s="17" t="str"/>
+      <x:c r="C13" s="17"/>
+      <x:c r="D13"/>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="17" t="str">
@@ -4845,7 +5719,8 @@
       <x:c r="B14" s="17" t="str">
         <x:v>Define clinical, operational, quality, accreditation, workforce, economic, equity, trust, environmental, and safety outcomes.</x:v>
       </x:c>
-      <x:c r="C14" s="17" t="str"/>
+      <x:c r="C14" s="17"/>
+      <x:c r="D14"/>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="17" t="str">
@@ -4854,7 +5729,8 @@
       <x:c r="B15" s="17" t="str">
         <x:v>State the analytic horizon and the time within which an output must lead to action.</x:v>
       </x:c>
-      <x:c r="C15" s="17" t="str"/>
+      <x:c r="C15" s="17"/>
+      <x:c r="D15"/>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="17" t="str">
@@ -4863,7 +5739,8 @@
       <x:c r="B16" s="17" t="str">
         <x:v>Explain how the intervention is expected to change a decision, action, outcome, resource consequence, and public value.</x:v>
       </x:c>
-      <x:c r="C16" s="17" t="str"/>
+      <x:c r="C16" s="17"/>
+      <x:c r="D16"/>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="17" t="str">
@@ -4872,7 +5749,8 @@
       <x:c r="B17" s="17" t="str">
         <x:v>Define proceed, redesign, silent validation, pilot, conditional adoption, scale, restrict, pause, replace, or retire criteria.</x:v>
       </x:c>
-      <x:c r="C17" s="17" t="str"/>
+      <x:c r="C17" s="17"/>
+      <x:c r="D17"/>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="17" t="str">
@@ -4881,15 +5759,17 @@
       <x:c r="B18" s="17" t="str">
         <x:v>Record the last evidence date, responsible reviewer, planned review date, and trigger events.</x:v>
       </x:c>
-      <x:c r="C18" s="17" t="str"/>
+      <x:c r="C18" s="17"/>
+      <x:c r="D18"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:F1"/>
+    <x:mergeCell ref="A1:D1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rab10837cc2f345e2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R853e8b47f9fa47be"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4905,23 +5785,29 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="29" t="str">
+      <x:c r="A1" s="78" t="str">
         <x:v>AIHE-A02 — Stakeholders, Decision Rights, and Participation</x:v>
       </x:c>
-      <x:c r="B1" s="29"/>
-      <x:c r="C1" s="29"/>
-      <x:c r="D1" s="29"/>
+      <x:c r="B1" s="78"/>
+      <x:c r="C1" s="78"/>
+      <x:c r="D1" s="78"/>
       <x:c r="E1" s="29"/>
       <x:c r="F1" s="29"/>
     </x:row>
+    <x:row r="2">
+      <x:c r="A2"/>
+      <x:c r="B2"/>
+      <x:c r="C2"/>
+      <x:c r="D2"/>
+    </x:row>
     <x:row r="3">
-      <x:c r="A3" s="33" t="str">
+      <x:c r="A3" s="80" t="str">
         <x:v>Primary chapter</x:v>
       </x:c>
       <x:c r="B3" s="17" t="str">
         <x:v>1 — AI as a Health-System Intervention</x:v>
       </x:c>
-      <x:c r="C3" s="33" t="str">
+      <x:c r="C3" s="80" t="str">
         <x:v>Release</x:v>
       </x:c>
       <x:c r="D3" s="17" t="str">
@@ -4929,13 +5815,13 @@
       </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="33" t="str">
+      <x:c r="A4" s="80" t="str">
         <x:v>Purpose</x:v>
       </x:c>
       <x:c r="B4" s="17" t="str">
         <x:v>Identify affected parties, decision rights, participation duties, evidence contributions, and escalation authority.</x:v>
       </x:c>
-      <x:c r="C4" s="33" t="str">
+      <x:c r="C4" s="80" t="str">
         <x:v>Reader level</x:v>
       </x:c>
       <x:c r="D4" s="17" t="str">
@@ -4943,13 +5829,13 @@
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="33" t="str">
+      <x:c r="A5" s="80" t="str">
         <x:v>Required inputs</x:v>
       </x:c>
       <x:c r="B5" s="17" t="str">
         <x:v>Defined decision problem, realistic comparator, local evidence, named owners, and applicable institutional requirements</x:v>
       </x:c>
-      <x:c r="C5" s="33" t="str">
+      <x:c r="C5" s="80" t="str">
         <x:v>Expected output</x:v>
       </x:c>
       <x:c r="D5" s="17" t="str">
@@ -4970,6 +5856,12 @@
         <x:v>60–180 minutes</x:v>
       </x:c>
     </x:row>
+    <x:row r="7">
+      <x:c r="A7"/>
+      <x:c r="B7"/>
+      <x:c r="C7"/>
+      <x:c r="D7"/>
+    </x:row>
     <x:row r="8">
       <x:c r="A8" s="23" t="str">
         <x:v>Role or group</x:v>
@@ -4994,7 +5886,7 @@
       <x:c r="C9" s="17" t="str">
         <x:v>Approve material commitment and named accountability</x:v>
       </x:c>
-      <x:c r="D9" s="17" t="str"/>
+      <x:c r="D9" s="17"/>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="17" t="str">
@@ -5006,7 +5898,7 @@
       <x:c r="C10" s="17" t="str">
         <x:v>Specify intended use, action, fallback, and clinical acceptance</x:v>
       </x:c>
-      <x:c r="D10" s="17" t="str"/>
+      <x:c r="D10" s="17"/>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="17" t="str">
@@ -5018,7 +5910,7 @@
       <x:c r="C11" s="17" t="str">
         <x:v>Integrate the intervention into quality-management and accreditation processes</x:v>
       </x:c>
-      <x:c r="D11" s="17" t="str"/>
+      <x:c r="D11" s="17"/>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="17" t="str">
@@ -5030,7 +5922,7 @@
       <x:c r="C12" s="17" t="str">
         <x:v>Approve economic methods, assumptions, and budget consequences</x:v>
       </x:c>
-      <x:c r="D12" s="17" t="str"/>
+      <x:c r="D12" s="17"/>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="17" t="str">
@@ -5042,7 +5934,7 @@
       <x:c r="C13" s="17" t="str">
         <x:v>Verify technical readiness and continuing operability</x:v>
       </x:c>
-      <x:c r="D13" s="17" t="str"/>
+      <x:c r="D13" s="17"/>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="17" t="str">
@@ -5054,7 +5946,7 @@
       <x:c r="C14" s="17" t="str">
         <x:v>Define mandatory safeguards and unresolved legal or ethical conditions</x:v>
       </x:c>
-      <x:c r="D14" s="17" t="str"/>
+      <x:c r="D14" s="17"/>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="17" t="str">
@@ -5066,7 +5958,7 @@
       <x:c r="C15" s="17" t="str">
         <x:v>Translate requirements into enforceable terms</x:v>
       </x:c>
-      <x:c r="D15" s="17" t="str"/>
+      <x:c r="D15" s="17"/>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="17" t="str">
@@ -5078,15 +5970,16 @@
       <x:c r="C16" s="17" t="str">
         <x:v>Contribute priorities, communication requirements, and challenge</x:v>
       </x:c>
-      <x:c r="D16" s="17" t="str"/>
+      <x:c r="D16" s="17"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:F1"/>
+    <x:mergeCell ref="A1:D1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2998a986c8ac41f3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R04eed9a5dba34667"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5102,23 +5995,29 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="29" t="str">
+      <x:c r="A1" s="78" t="str">
         <x:v>AIHE-A03 — Institutional Readiness Assessment</x:v>
       </x:c>
-      <x:c r="B1" s="29"/>
-      <x:c r="C1" s="29"/>
-      <x:c r="D1" s="29"/>
+      <x:c r="B1" s="78"/>
+      <x:c r="C1" s="78"/>
+      <x:c r="D1" s="78"/>
       <x:c r="E1" s="29"/>
       <x:c r="F1" s="29"/>
     </x:row>
+    <x:row r="2">
+      <x:c r="A2"/>
+      <x:c r="B2"/>
+      <x:c r="C2"/>
+      <x:c r="D2"/>
+    </x:row>
     <x:row r="3">
-      <x:c r="A3" s="33" t="str">
+      <x:c r="A3" s="80" t="str">
         <x:v>Primary chapter</x:v>
       </x:c>
       <x:c r="B3" s="17" t="str">
         <x:v>2 — Institutional Readiness and Digital Foundations</x:v>
       </x:c>
-      <x:c r="C3" s="33" t="str">
+      <x:c r="C3" s="80" t="str">
         <x:v>Release</x:v>
       </x:c>
       <x:c r="D3" s="17" t="str">
@@ -5126,13 +6025,13 @@
       </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="33" t="str">
+      <x:c r="A4" s="80" t="str">
         <x:v>Purpose</x:v>
       </x:c>
       <x:c r="B4" s="17" t="str">
         <x:v>Assess strategic, data, infrastructure, workflow, workforce, quality, economic, governance, procurement, and sustainability readiness.</x:v>
       </x:c>
-      <x:c r="C4" s="33" t="str">
+      <x:c r="C4" s="80" t="str">
         <x:v>Reader level</x:v>
       </x:c>
       <x:c r="D4" s="17" t="str">
@@ -5140,13 +6039,13 @@
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="33" t="str">
+      <x:c r="A5" s="80" t="str">
         <x:v>Required inputs</x:v>
       </x:c>
       <x:c r="B5" s="17" t="str">
         <x:v>Defined decision problem, realistic comparator, local evidence, named owners, and applicable institutional requirements</x:v>
       </x:c>
-      <x:c r="C5" s="33" t="str">
+      <x:c r="C5" s="80" t="str">
         <x:v>Expected output</x:v>
       </x:c>
       <x:c r="D5" s="17" t="str">
@@ -5167,6 +6066,12 @@
         <x:v>60–180 minutes</x:v>
       </x:c>
     </x:row>
+    <x:row r="7">
+      <x:c r="A7"/>
+      <x:c r="B7"/>
+      <x:c r="C7"/>
+      <x:c r="D7"/>
+    </x:row>
     <x:row r="8">
       <x:c r="A8" s="23" t="str">
         <x:v>Domain</x:v>
@@ -5188,8 +6093,8 @@
       <x:c r="B9" s="17" t="str">
         <x:v>Is the problem linked to documented health-system priorities and realistic alternatives?</x:v>
       </x:c>
-      <x:c r="C9" s="17" t="str"/>
-      <x:c r="D9" s="17" t="str"/>
+      <x:c r="C9" s="17"/>
+      <x:c r="D9" s="17"/>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="17" t="str">
@@ -5198,8 +6103,8 @@
       <x:c r="B10" s="17" t="str">
         <x:v>Are required data lawful, available, timely, representative, traceable, and sustainable?</x:v>
       </x:c>
-      <x:c r="C10" s="17" t="str"/>
-      <x:c r="D10" s="17" t="str"/>
+      <x:c r="C10" s="17"/>
+      <x:c r="D10" s="17"/>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="17" t="str">
@@ -5208,8 +6113,8 @@
       <x:c r="B11" s="17" t="str">
         <x:v>Can inputs and outputs be exchanged and interpreted consistently within the decision window?</x:v>
       </x:c>
-      <x:c r="C11" s="17" t="str"/>
-      <x:c r="D11" s="17" t="str"/>
+      <x:c r="C11" s="17"/>
+      <x:c r="D11" s="17"/>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="17" t="str">
@@ -5218,8 +6123,8 @@
       <x:c r="B12" s="17" t="str">
         <x:v>Are identity, access, compute, storage, interfaces, logging, fallback, and recovery adequate?</x:v>
       </x:c>
-      <x:c r="C12" s="17" t="str"/>
-      <x:c r="D12" s="17" t="str"/>
+      <x:c r="C12" s="17"/>
+      <x:c r="D12" s="17"/>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="17" t="str">
@@ -5228,8 +6133,8 @@
       <x:c r="B13" s="17" t="str">
         <x:v>Can users interpret the output and take the intended action without shifting unsafe burden?</x:v>
       </x:c>
-      <x:c r="C13" s="17" t="str"/>
-      <x:c r="D13" s="17" t="str"/>
+      <x:c r="C13" s="17"/>
+      <x:c r="D13" s="17"/>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="17" t="str">
@@ -5238,8 +6143,8 @@
       <x:c r="B14" s="17" t="str">
         <x:v>Are roles, training, competency, supervision, and professional responsibilities defined?</x:v>
       </x:c>
-      <x:c r="C14" s="17" t="str"/>
-      <x:c r="D14" s="17" t="str"/>
+      <x:c r="C14" s="17"/>
+      <x:c r="D14" s="17"/>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="17" t="str">
@@ -5248,8 +6153,8 @@
       <x:c r="B15" s="17" t="str">
         <x:v>Are controls, indicators, evidence, incident processes, and improvement responsibilities integrated?</x:v>
       </x:c>
-      <x:c r="C15" s="17" t="str"/>
-      <x:c r="D15" s="17" t="str"/>
+      <x:c r="C15" s="17"/>
+      <x:c r="D15" s="17"/>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="17" t="str">
@@ -5258,8 +6163,8 @@
       <x:c r="B16" s="17" t="str">
         <x:v>Are lifecycle costs, resource constraints, benefits, uncertainty, and budget exposure understood?</x:v>
       </x:c>
-      <x:c r="C16" s="17" t="str"/>
-      <x:c r="D16" s="17" t="str"/>
+      <x:c r="C16" s="17"/>
+      <x:c r="D16" s="17"/>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="17" t="str">
@@ -5268,8 +6173,8 @@
       <x:c r="B17" s="17" t="str">
         <x:v>Are decision rights, safeguards, independent review, monitoring, and authority to stop defined?</x:v>
       </x:c>
-      <x:c r="C17" s="17" t="str"/>
-      <x:c r="D17" s="17" t="str"/>
+      <x:c r="C17" s="17"/>
+      <x:c r="D17" s="17"/>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="17" t="str">
@@ -5278,8 +6183,8 @@
       <x:c r="B18" s="17" t="str">
         <x:v>Can evidence, audit, updates, data rights, support, pricing, portability, and exit be contracted?</x:v>
       </x:c>
-      <x:c r="C18" s="17" t="str"/>
-      <x:c r="D18" s="17" t="str"/>
+      <x:c r="C18" s="17"/>
+      <x:c r="D18" s="17"/>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="17" t="str">
@@ -5288,16 +6193,17 @@
       <x:c r="B19" s="17" t="str">
         <x:v>Are resource demand, asset life, maintenance, take-back, residual value, and disposition considered where material?</x:v>
       </x:c>
-      <x:c r="C19" s="17" t="str"/>
-      <x:c r="D19" s="17" t="str"/>
+      <x:c r="C19" s="17"/>
+      <x:c r="D19" s="17"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:F1"/>
+    <x:mergeCell ref="A1:D1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re88b0f800d084172"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf66df757192848a6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5316,57 +6222,75 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="29" t="str">
+      <x:c r="A1" s="78" t="str">
         <x:v>AIHE-A04 — Data Source, Provenance, and Fitness Record</x:v>
       </x:c>
-      <x:c r="B1" s="29"/>
-      <x:c r="C1" s="29"/>
-      <x:c r="D1" s="29"/>
-      <x:c r="E1" s="29"/>
-      <x:c r="F1" s="29"/>
-      <x:c r="G1" s="29"/>
+      <x:c r="B1" s="78"/>
+      <x:c r="C1" s="78"/>
+      <x:c r="D1" s="78"/>
+      <x:c r="E1" s="78"/>
+      <x:c r="F1" s="78"/>
+      <x:c r="G1" s="78"/>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2"/>
+      <x:c r="B2"/>
+      <x:c r="C2"/>
+      <x:c r="D2"/>
+      <x:c r="E2"/>
+      <x:c r="F2"/>
+      <x:c r="G2"/>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="33" t="str">
+      <x:c r="A3" s="80" t="str">
         <x:v>Primary chapter</x:v>
       </x:c>
       <x:c r="B3" s="17" t="str">
         <x:v>2 — Institutional Readiness and Digital Foundations</x:v>
       </x:c>
-      <x:c r="C3" s="33" t="str">
+      <x:c r="C3" s="80" t="str">
         <x:v>Release</x:v>
       </x:c>
       <x:c r="D3" s="17" t="str">
         <x:v>V1.0</x:v>
       </x:c>
+      <x:c r="E3"/>
+      <x:c r="F3"/>
+      <x:c r="G3"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="33" t="str">
+      <x:c r="A4" s="80" t="str">
         <x:v>Purpose</x:v>
       </x:c>
       <x:c r="B4" s="17" t="str">
         <x:v>Document source and derived data assets, authority, definitions, transformations, quality, lineage, monitoring, and remediation.</x:v>
       </x:c>
-      <x:c r="C4" s="33" t="str">
+      <x:c r="C4" s="80" t="str">
         <x:v>Reader level</x:v>
       </x:c>
       <x:c r="D4" s="17" t="str">
         <x:v>Applied</x:v>
       </x:c>
+      <x:c r="E4"/>
+      <x:c r="F4"/>
+      <x:c r="G4"/>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="33" t="str">
+      <x:c r="A5" s="80" t="str">
         <x:v>Required inputs</x:v>
       </x:c>
       <x:c r="B5" s="17" t="str">
         <x:v>Defined decision problem, realistic comparator, local evidence, named owners, and applicable institutional requirements</x:v>
       </x:c>
-      <x:c r="C5" s="33" t="str">
+      <x:c r="C5" s="80" t="str">
         <x:v>Expected output</x:v>
       </x:c>
       <x:c r="D5" s="17" t="str">
         <x:v>Versioned institutional decision record with conditions, monitoring, review date, and exit route</x:v>
       </x:c>
+      <x:c r="E5"/>
+      <x:c r="F5"/>
+      <x:c r="G5"/>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="33" t="str">
@@ -5381,6 +6305,18 @@
       <x:c r="D6" s="17" t="str">
         <x:v>60–180 minutes</x:v>
       </x:c>
+      <x:c r="E6"/>
+      <x:c r="F6"/>
+      <x:c r="G6"/>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7"/>
+      <x:c r="B7"/>
+      <x:c r="C7"/>
+      <x:c r="D7"/>
+      <x:c r="E7"/>
+      <x:c r="F7"/>
+      <x:c r="G7"/>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="23" t="str">
@@ -5438,7 +6374,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcf055f8db8fd436f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R64aec6fb5a194a12"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5458,58 +6394,80 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="29" t="str">
+      <x:c r="A1" s="78" t="str">
         <x:v>AIHE-C04 — Human Oversight and Accountability Matrix</x:v>
       </x:c>
-      <x:c r="B1" s="29"/>
-      <x:c r="C1" s="29"/>
-      <x:c r="D1" s="29"/>
-      <x:c r="E1" s="29"/>
-      <x:c r="F1" s="29"/>
-      <x:c r="G1" s="29"/>
-      <x:c r="H1" s="29"/>
+      <x:c r="B1" s="78"/>
+      <x:c r="C1" s="78"/>
+      <x:c r="D1" s="78"/>
+      <x:c r="E1" s="78"/>
+      <x:c r="F1" s="78"/>
+      <x:c r="G1" s="78"/>
+      <x:c r="H1" s="78"/>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2"/>
+      <x:c r="B2"/>
+      <x:c r="C2"/>
+      <x:c r="D2"/>
+      <x:c r="E2"/>
+      <x:c r="F2"/>
+      <x:c r="G2"/>
+      <x:c r="H2"/>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="33" t="str">
+      <x:c r="A3" s="80" t="str">
         <x:v>Primary chapter</x:v>
       </x:c>
       <x:c r="B3" s="17" t="str">
         <x:v>3 — Human–AI Decision Support and Managerial Action</x:v>
       </x:c>
-      <x:c r="C3" s="33" t="str">
+      <x:c r="C3" s="80" t="str">
         <x:v>Release</x:v>
       </x:c>
       <x:c r="D3" s="17" t="str">
         <x:v>V1.0</x:v>
       </x:c>
+      <x:c r="E3"/>
+      <x:c r="F3"/>
+      <x:c r="G3"/>
+      <x:c r="H3"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="33" t="str">
+      <x:c r="A4" s="80" t="str">
         <x:v>Purpose</x:v>
       </x:c>
       <x:c r="B4" s="17" t="str">
         <x:v>Assign accountability, responsibility, consultation, information, escalation, pause, update, restart, and retirement authority.</x:v>
       </x:c>
-      <x:c r="C4" s="33" t="str">
+      <x:c r="C4" s="80" t="str">
         <x:v>Reader level</x:v>
       </x:c>
       <x:c r="D4" s="17" t="str">
         <x:v>Applied</x:v>
       </x:c>
+      <x:c r="E4"/>
+      <x:c r="F4"/>
+      <x:c r="G4"/>
+      <x:c r="H4"/>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="33" t="str">
+      <x:c r="A5" s="80" t="str">
         <x:v>Required inputs</x:v>
       </x:c>
       <x:c r="B5" s="17" t="str">
         <x:v>Defined decision problem, realistic comparator, local evidence, named owners, and applicable institutional requirements</x:v>
       </x:c>
-      <x:c r="C5" s="33" t="str">
+      <x:c r="C5" s="80" t="str">
         <x:v>Expected output</x:v>
       </x:c>
       <x:c r="D5" s="17" t="str">
         <x:v>Versioned institutional decision record with conditions, monitoring, review date, and exit route</x:v>
       </x:c>
+      <x:c r="E5"/>
+      <x:c r="F5"/>
+      <x:c r="G5"/>
+      <x:c r="H5"/>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="33" t="str">
@@ -5524,6 +6482,20 @@
       <x:c r="D6" s="17" t="str">
         <x:v>60–180 minutes</x:v>
       </x:c>
+      <x:c r="E6"/>
+      <x:c r="F6"/>
+      <x:c r="G6"/>
+      <x:c r="H6"/>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7"/>
+      <x:c r="B7"/>
+      <x:c r="C7"/>
+      <x:c r="D7"/>
+      <x:c r="E7"/>
+      <x:c r="F7"/>
+      <x:c r="G7"/>
+      <x:c r="H7"/>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="23" t="str">
@@ -5555,97 +6527,97 @@
       <x:c r="A9" s="17" t="str">
         <x:v>Define problem, comparator, and intended use</x:v>
       </x:c>
-      <x:c r="B9" s="17" t="str"/>
-      <x:c r="C9" s="17" t="str"/>
-      <x:c r="D9" s="17" t="str"/>
-      <x:c r="E9" s="17" t="str"/>
-      <x:c r="F9" s="17" t="str"/>
-      <x:c r="G9" s="17" t="str"/>
-      <x:c r="H9" s="17" t="str"/>
+      <x:c r="B9" s="17"/>
+      <x:c r="C9" s="17"/>
+      <x:c r="D9" s="17"/>
+      <x:c r="E9" s="17"/>
+      <x:c r="F9" s="17"/>
+      <x:c r="G9" s="17"/>
+      <x:c r="H9" s="17"/>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="17" t="str">
         <x:v>Assess evidence, data, and local validity</x:v>
       </x:c>
-      <x:c r="B10" s="17" t="str"/>
-      <x:c r="C10" s="17" t="str"/>
-      <x:c r="D10" s="17" t="str"/>
-      <x:c r="E10" s="17" t="str"/>
-      <x:c r="F10" s="17" t="str"/>
-      <x:c r="G10" s="17" t="str"/>
-      <x:c r="H10" s="17" t="str"/>
+      <x:c r="B10" s="17"/>
+      <x:c r="C10" s="17"/>
+      <x:c r="D10" s="17"/>
+      <x:c r="E10" s="17"/>
+      <x:c r="F10" s="17"/>
+      <x:c r="G10" s="17"/>
+      <x:c r="H10" s="17"/>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="17" t="str">
         <x:v>Conduct economic and affordability analysis</x:v>
       </x:c>
-      <x:c r="B11" s="17" t="str"/>
-      <x:c r="C11" s="17" t="str"/>
-      <x:c r="D11" s="17" t="str"/>
-      <x:c r="E11" s="17" t="str"/>
-      <x:c r="F11" s="17" t="str"/>
-      <x:c r="G11" s="17" t="str"/>
-      <x:c r="H11" s="17" t="str"/>
+      <x:c r="B11" s="17"/>
+      <x:c r="C11" s="17"/>
+      <x:c r="D11" s="17"/>
+      <x:c r="E11" s="17"/>
+      <x:c r="F11" s="17"/>
+      <x:c r="G11" s="17"/>
+      <x:c r="H11" s="17"/>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="17" t="str">
         <x:v>Approve procurement, contract, and pilot</x:v>
       </x:c>
-      <x:c r="B12" s="17" t="str"/>
-      <x:c r="C12" s="17" t="str"/>
-      <x:c r="D12" s="17" t="str"/>
-      <x:c r="E12" s="17" t="str"/>
-      <x:c r="F12" s="17" t="str"/>
-      <x:c r="G12" s="17" t="str"/>
-      <x:c r="H12" s="17" t="str"/>
+      <x:c r="B12" s="17"/>
+      <x:c r="C12" s="17"/>
+      <x:c r="D12" s="17"/>
+      <x:c r="E12" s="17"/>
+      <x:c r="F12" s="17"/>
+      <x:c r="G12" s="17"/>
+      <x:c r="H12" s="17"/>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="17" t="str">
         <x:v>Operate, review, override, and escalate</x:v>
       </x:c>
-      <x:c r="B13" s="17" t="str"/>
-      <x:c r="C13" s="17" t="str"/>
-      <x:c r="D13" s="17" t="str"/>
-      <x:c r="E13" s="17" t="str"/>
-      <x:c r="F13" s="17" t="str"/>
-      <x:c r="G13" s="17" t="str"/>
-      <x:c r="H13" s="17" t="str"/>
+      <x:c r="B13" s="17"/>
+      <x:c r="C13" s="17"/>
+      <x:c r="D13" s="17"/>
+      <x:c r="E13" s="17"/>
+      <x:c r="F13" s="17"/>
+      <x:c r="G13" s="17"/>
+      <x:c r="H13" s="17"/>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="17" t="str">
         <x:v>Investigate incidents and corrective action</x:v>
       </x:c>
-      <x:c r="B14" s="17" t="str"/>
-      <x:c r="C14" s="17" t="str"/>
-      <x:c r="D14" s="17" t="str"/>
-      <x:c r="E14" s="17" t="str"/>
-      <x:c r="F14" s="17" t="str"/>
-      <x:c r="G14" s="17" t="str"/>
-      <x:c r="H14" s="17" t="str"/>
+      <x:c r="B14" s="17"/>
+      <x:c r="C14" s="17"/>
+      <x:c r="D14" s="17"/>
+      <x:c r="E14" s="17"/>
+      <x:c r="F14" s="17"/>
+      <x:c r="G14" s="17"/>
+      <x:c r="H14" s="17"/>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="17" t="str">
         <x:v>Approve material change or expansion</x:v>
       </x:c>
-      <x:c r="B15" s="17" t="str"/>
-      <x:c r="C15" s="17" t="str"/>
-      <x:c r="D15" s="17" t="str"/>
-      <x:c r="E15" s="17" t="str"/>
-      <x:c r="F15" s="17" t="str"/>
-      <x:c r="G15" s="17" t="str"/>
-      <x:c r="H15" s="17" t="str"/>
+      <x:c r="B15" s="17"/>
+      <x:c r="C15" s="17"/>
+      <x:c r="D15" s="17"/>
+      <x:c r="E15" s="17"/>
+      <x:c r="F15" s="17"/>
+      <x:c r="G15" s="17"/>
+      <x:c r="H15" s="17"/>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="17" t="str">
         <x:v>Renew, restrict, replace, pause, restart, or retire</x:v>
       </x:c>
-      <x:c r="B16" s="17" t="str"/>
-      <x:c r="C16" s="17" t="str"/>
-      <x:c r="D16" s="17" t="str"/>
-      <x:c r="E16" s="17" t="str"/>
-      <x:c r="F16" s="17" t="str"/>
-      <x:c r="G16" s="17" t="str"/>
-      <x:c r="H16" s="17" t="str"/>
+      <x:c r="B16" s="17"/>
+      <x:c r="C16" s="17"/>
+      <x:c r="D16" s="17"/>
+      <x:c r="E16" s="17"/>
+      <x:c r="F16" s="17"/>
+      <x:c r="G16" s="17"/>
+      <x:c r="H16" s="17"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -5653,7 +6625,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R259f43f780e84c1f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R65c7ccd551dc47f0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5670,56 +6642,66 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="29" t="str">
+      <x:c r="A1" s="78" t="str">
         <x:v>AIHE-B03 — Benefit Realization and Capacity Conversion</x:v>
       </x:c>
-      <x:c r="B1" s="29"/>
-      <x:c r="C1" s="29"/>
-      <x:c r="D1" s="29"/>
-      <x:c r="E1" s="29"/>
+      <x:c r="B1" s="78"/>
+      <x:c r="C1" s="78"/>
+      <x:c r="D1" s="78"/>
+      <x:c r="E1" s="78"/>
       <x:c r="F1" s="29"/>
     </x:row>
+    <x:row r="2">
+      <x:c r="A2"/>
+      <x:c r="B2"/>
+      <x:c r="C2"/>
+      <x:c r="D2"/>
+      <x:c r="E2"/>
+    </x:row>
     <x:row r="3">
-      <x:c r="A3" s="33" t="str">
+      <x:c r="A3" s="80" t="str">
         <x:v>Primary chapter</x:v>
       </x:c>
       <x:c r="B3" s="17" t="str">
         <x:v>4 — Productivity, Workforce Redesign, and Implementation</x:v>
       </x:c>
-      <x:c r="C3" s="33" t="str">
+      <x:c r="C3" s="80" t="str">
         <x:v>Release</x:v>
       </x:c>
       <x:c r="D3" s="17" t="str">
         <x:v>V1.0</x:v>
       </x:c>
+      <x:c r="E3"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="33" t="str">
+      <x:c r="A4" s="80" t="str">
         <x:v>Purpose</x:v>
       </x:c>
       <x:c r="B4" s="17" t="str">
         <x:v>Translate claimed benefits into measurable mechanisms, owners, baselines, conversion conditions, and realized results.</x:v>
       </x:c>
-      <x:c r="C4" s="33" t="str">
+      <x:c r="C4" s="80" t="str">
         <x:v>Reader level</x:v>
       </x:c>
       <x:c r="D4" s="17" t="str">
         <x:v>Applied</x:v>
       </x:c>
+      <x:c r="E4"/>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="33" t="str">
+      <x:c r="A5" s="80" t="str">
         <x:v>Required inputs</x:v>
       </x:c>
       <x:c r="B5" s="17" t="str">
         <x:v>Defined decision problem, realistic comparator, local evidence, named owners, and applicable institutional requirements</x:v>
       </x:c>
-      <x:c r="C5" s="33" t="str">
+      <x:c r="C5" s="80" t="str">
         <x:v>Expected output</x:v>
       </x:c>
       <x:c r="D5" s="17" t="str">
         <x:v>Versioned institutional decision record with conditions, monitoring, review date, and exit route</x:v>
       </x:c>
+      <x:c r="E5"/>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="33" t="str">
@@ -5734,6 +6716,14 @@
       <x:c r="D6" s="17" t="str">
         <x:v>60–180 minutes</x:v>
       </x:c>
+      <x:c r="E6"/>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7"/>
+      <x:c r="B7"/>
+      <x:c r="C7"/>
+      <x:c r="D7"/>
+      <x:c r="E7"/>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="23" t="str">
@@ -5776,10 +6766,11 @@
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:F1"/>
+    <x:mergeCell ref="A1:E1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R50b3c3035a594339"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R59c08c2d37814b41"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5798,57 +6789,75 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="29" t="str">
+      <x:c r="A1" s="78" t="str">
         <x:v>AIHE-C01 — AI Quality-Control and Accreditation Evidence Plan</x:v>
       </x:c>
-      <x:c r="B1" s="29"/>
-      <x:c r="C1" s="29"/>
-      <x:c r="D1" s="29"/>
-      <x:c r="E1" s="29"/>
-      <x:c r="F1" s="29"/>
-      <x:c r="G1" s="29"/>
+      <x:c r="B1" s="78"/>
+      <x:c r="C1" s="78"/>
+      <x:c r="D1" s="78"/>
+      <x:c r="E1" s="78"/>
+      <x:c r="F1" s="78"/>
+      <x:c r="G1" s="78"/>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2"/>
+      <x:c r="B2"/>
+      <x:c r="C2"/>
+      <x:c r="D2"/>
+      <x:c r="E2"/>
+      <x:c r="F2"/>
+      <x:c r="G2"/>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="33" t="str">
+      <x:c r="A3" s="80" t="str">
         <x:v>Primary chapter</x:v>
       </x:c>
       <x:c r="B3" s="17" t="str">
         <x:v>5 — Quality, Accreditation, and Organizational Learning</x:v>
       </x:c>
-      <x:c r="C3" s="33" t="str">
+      <x:c r="C3" s="80" t="str">
         <x:v>Release</x:v>
       </x:c>
       <x:c r="D3" s="17" t="str">
         <x:v>V1.0</x:v>
       </x:c>
+      <x:c r="E3"/>
+      <x:c r="F3"/>
+      <x:c r="G3"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="33" t="str">
+      <x:c r="A4" s="80" t="str">
         <x:v>Purpose</x:v>
       </x:c>
       <x:c r="B4" s="17" t="str">
         <x:v>Integrate AI-enabled services into quality control, accreditation evidence, monitoring, thresholds, action, and closure.</x:v>
       </x:c>
-      <x:c r="C4" s="33" t="str">
+      <x:c r="C4" s="80" t="str">
         <x:v>Reader level</x:v>
       </x:c>
       <x:c r="D4" s="17" t="str">
         <x:v>Applied</x:v>
       </x:c>
+      <x:c r="E4"/>
+      <x:c r="F4"/>
+      <x:c r="G4"/>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="33" t="str">
+      <x:c r="A5" s="80" t="str">
         <x:v>Required inputs</x:v>
       </x:c>
       <x:c r="B5" s="17" t="str">
         <x:v>Defined decision problem, realistic comparator, local evidence, named owners, and applicable institutional requirements</x:v>
       </x:c>
-      <x:c r="C5" s="33" t="str">
+      <x:c r="C5" s="80" t="str">
         <x:v>Expected output</x:v>
       </x:c>
       <x:c r="D5" s="17" t="str">
         <x:v>Versioned institutional decision record with conditions, monitoring, review date, and exit route</x:v>
       </x:c>
+      <x:c r="E5"/>
+      <x:c r="F5"/>
+      <x:c r="G5"/>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="33" t="str">
@@ -5863,6 +6872,18 @@
       <x:c r="D6" s="17" t="str">
         <x:v>60–180 minutes</x:v>
       </x:c>
+      <x:c r="E6"/>
+      <x:c r="F6"/>
+      <x:c r="G6"/>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7"/>
+      <x:c r="B7"/>
+      <x:c r="C7"/>
+      <x:c r="D7"/>
+      <x:c r="E7"/>
+      <x:c r="F7"/>
+      <x:c r="G7"/>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="23" t="str">
@@ -5891,89 +6912,89 @@
       <x:c r="A9" s="17" t="str">
         <x:v>Technical reliability</x:v>
       </x:c>
-      <x:c r="B9" s="17" t="str"/>
-      <x:c r="C9" s="17" t="str"/>
-      <x:c r="D9" s="17" t="str"/>
-      <x:c r="E9" s="17" t="str"/>
-      <x:c r="F9" s="17" t="str"/>
-      <x:c r="G9" s="17" t="str"/>
+      <x:c r="B9" s="17"/>
+      <x:c r="C9" s="17"/>
+      <x:c r="D9" s="17"/>
+      <x:c r="E9" s="17"/>
+      <x:c r="F9" s="17"/>
+      <x:c r="G9" s="17"/>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="17" t="str">
         <x:v>Model and human–AI performance</x:v>
       </x:c>
-      <x:c r="B10" s="17" t="str"/>
-      <x:c r="C10" s="17" t="str"/>
-      <x:c r="D10" s="17" t="str"/>
-      <x:c r="E10" s="17" t="str"/>
-      <x:c r="F10" s="17" t="str"/>
-      <x:c r="G10" s="17" t="str"/>
+      <x:c r="B10" s="17"/>
+      <x:c r="C10" s="17"/>
+      <x:c r="D10" s="17"/>
+      <x:c r="E10" s="17"/>
+      <x:c r="F10" s="17"/>
+      <x:c r="G10" s="17"/>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="17" t="str">
         <x:v>Clinical safety and outcome</x:v>
       </x:c>
-      <x:c r="B11" s="17" t="str"/>
-      <x:c r="C11" s="17" t="str"/>
-      <x:c r="D11" s="17" t="str"/>
-      <x:c r="E11" s="17" t="str"/>
-      <x:c r="F11" s="17" t="str"/>
-      <x:c r="G11" s="17" t="str"/>
+      <x:c r="B11" s="17"/>
+      <x:c r="C11" s="17"/>
+      <x:c r="D11" s="17"/>
+      <x:c r="E11" s="17"/>
+      <x:c r="F11" s="17"/>
+      <x:c r="G11" s="17"/>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="17" t="str">
         <x:v>Workflow and professional practice</x:v>
       </x:c>
-      <x:c r="B12" s="17" t="str"/>
-      <x:c r="C12" s="17" t="str"/>
-      <x:c r="D12" s="17" t="str"/>
-      <x:c r="E12" s="17" t="str"/>
-      <x:c r="F12" s="17" t="str"/>
-      <x:c r="G12" s="17" t="str"/>
+      <x:c r="B12" s="17"/>
+      <x:c r="C12" s="17"/>
+      <x:c r="D12" s="17"/>
+      <x:c r="E12" s="17"/>
+      <x:c r="F12" s="17"/>
+      <x:c r="G12" s="17"/>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="17" t="str">
         <x:v>Patient experience and communication</x:v>
       </x:c>
-      <x:c r="B13" s="17" t="str"/>
-      <x:c r="C13" s="17" t="str"/>
-      <x:c r="D13" s="17" t="str"/>
-      <x:c r="E13" s="17" t="str"/>
-      <x:c r="F13" s="17" t="str"/>
-      <x:c r="G13" s="17" t="str"/>
+      <x:c r="B13" s="17"/>
+      <x:c r="C13" s="17"/>
+      <x:c r="D13" s="17"/>
+      <x:c r="E13" s="17"/>
+      <x:c r="F13" s="17"/>
+      <x:c r="G13" s="17"/>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="17" t="str">
         <x:v>Equity and access</x:v>
       </x:c>
-      <x:c r="B14" s="17" t="str"/>
-      <x:c r="C14" s="17" t="str"/>
-      <x:c r="D14" s="17" t="str"/>
-      <x:c r="E14" s="17" t="str"/>
-      <x:c r="F14" s="17" t="str"/>
-      <x:c r="G14" s="17" t="str"/>
+      <x:c r="B14" s="17"/>
+      <x:c r="C14" s="17"/>
+      <x:c r="D14" s="17"/>
+      <x:c r="E14" s="17"/>
+      <x:c r="F14" s="17"/>
+      <x:c r="G14" s="17"/>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="17" t="str">
         <x:v>Economic and resource value</x:v>
       </x:c>
-      <x:c r="B15" s="17" t="str"/>
-      <x:c r="C15" s="17" t="str"/>
-      <x:c r="D15" s="17" t="str"/>
-      <x:c r="E15" s="17" t="str"/>
-      <x:c r="F15" s="17" t="str"/>
-      <x:c r="G15" s="17" t="str"/>
+      <x:c r="B15" s="17"/>
+      <x:c r="C15" s="17"/>
+      <x:c r="D15" s="17"/>
+      <x:c r="E15" s="17"/>
+      <x:c r="F15" s="17"/>
+      <x:c r="G15" s="17"/>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="17" t="str">
         <x:v>Governance and documentation</x:v>
       </x:c>
-      <x:c r="B16" s="17" t="str"/>
-      <x:c r="C16" s="17" t="str"/>
-      <x:c r="D16" s="17" t="str"/>
-      <x:c r="E16" s="17" t="str"/>
-      <x:c r="F16" s="17" t="str"/>
-      <x:c r="G16" s="17" t="str"/>
+      <x:c r="B16" s="17"/>
+      <x:c r="C16" s="17"/>
+      <x:c r="D16" s="17"/>
+      <x:c r="E16" s="17"/>
+      <x:c r="F16" s="17"/>
+      <x:c r="G16" s="17"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -5981,7 +7002,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re65642faa2294f6e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbd3efbe106994fad"/>
   </x:tableParts>
 </x:worksheet>
 </file>